--- a/AAII_Financials/Quarterly/ANZGY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ANZGY_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
@@ -716,25 +716,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>17510400</v>
+        <v>17808100</v>
       </c>
       <c r="E8" s="3">
-        <v>14776200</v>
+        <v>15027400</v>
       </c>
       <c r="F8" s="3">
-        <v>8994600</v>
+        <v>9147500</v>
       </c>
       <c r="G8" s="3">
-        <v>6280400</v>
+        <v>6387200</v>
       </c>
       <c r="H8" s="3">
-        <v>6243600</v>
+        <v>6349700</v>
       </c>
       <c r="I8" s="3">
-        <v>6391700</v>
+        <v>6500400</v>
       </c>
       <c r="J8" s="3">
-        <v>6875000</v>
+        <v>6991900</v>
       </c>
       <c r="K8" s="3">
         <v>8946500</v>
@@ -941,25 +941,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-161100</v>
+        <v>-163800</v>
       </c>
       <c r="E15" s="3">
-        <v>-165600</v>
+        <v>-168400</v>
       </c>
       <c r="F15" s="3">
-        <v>-184400</v>
+        <v>-187500</v>
       </c>
       <c r="G15" s="3">
-        <v>-189600</v>
+        <v>-192800</v>
       </c>
       <c r="H15" s="3">
-        <v>-196700</v>
+        <v>-200000</v>
       </c>
       <c r="I15" s="3">
-        <v>-216100</v>
+        <v>-219800</v>
       </c>
       <c r="J15" s="3">
-        <v>-334500</v>
+        <v>-340200</v>
       </c>
       <c r="K15" s="3">
         <v>-221100</v>
@@ -988,25 +988,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>12354500</v>
+        <v>12564500</v>
       </c>
       <c r="E17" s="3">
-        <v>9362700</v>
+        <v>9521900</v>
       </c>
       <c r="F17" s="3">
-        <v>3998500</v>
+        <v>4066400</v>
       </c>
       <c r="G17" s="3">
-        <v>1503000</v>
+        <v>1528500</v>
       </c>
       <c r="H17" s="3">
-        <v>1552200</v>
+        <v>1578500</v>
       </c>
       <c r="I17" s="3">
-        <v>1554100</v>
+        <v>1580500</v>
       </c>
       <c r="J17" s="3">
-        <v>3146400</v>
+        <v>3199900</v>
       </c>
       <c r="K17" s="3">
         <v>5349800</v>
@@ -1023,25 +1023,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>5155900</v>
+        <v>5243600</v>
       </c>
       <c r="E18" s="3">
-        <v>5413400</v>
+        <v>5505500</v>
       </c>
       <c r="F18" s="3">
-        <v>4996100</v>
+        <v>5081100</v>
       </c>
       <c r="G18" s="3">
-        <v>4777400</v>
+        <v>4858700</v>
       </c>
       <c r="H18" s="3">
-        <v>4691400</v>
+        <v>4771200</v>
       </c>
       <c r="I18" s="3">
-        <v>4837600</v>
+        <v>4919900</v>
       </c>
       <c r="J18" s="3">
-        <v>3728700</v>
+        <v>3792100</v>
       </c>
       <c r="K18" s="3">
         <v>3596800</v>
@@ -1073,25 +1073,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-1890500</v>
+        <v>-1922700</v>
       </c>
       <c r="E20" s="3">
-        <v>-2160300</v>
+        <v>-2197100</v>
       </c>
       <c r="F20" s="3">
-        <v>-1732700</v>
+        <v>-1762100</v>
       </c>
       <c r="G20" s="3">
-        <v>-1519800</v>
+        <v>-1545600</v>
       </c>
       <c r="H20" s="3">
-        <v>-1741100</v>
+        <v>-1770700</v>
       </c>
       <c r="I20" s="3">
-        <v>-2006300</v>
+        <v>-2040500</v>
       </c>
       <c r="J20" s="3">
-        <v>-1851100</v>
+        <v>-1882500</v>
       </c>
       <c r="K20" s="3">
         <v>-1902100</v>
@@ -1108,25 +1108,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>3557900</v>
+        <v>3618300</v>
       </c>
       <c r="E21" s="3">
-        <v>3557900</v>
+        <v>3618300</v>
       </c>
       <c r="F21" s="3">
-        <v>3586300</v>
+        <v>3647300</v>
       </c>
       <c r="G21" s="3">
-        <v>3587000</v>
+        <v>3648000</v>
       </c>
       <c r="H21" s="3">
-        <v>3289300</v>
+        <v>3345300</v>
       </c>
       <c r="I21" s="3">
-        <v>3195500</v>
+        <v>3249900</v>
       </c>
       <c r="J21" s="3">
-        <v>2381000</v>
+        <v>2421400</v>
       </c>
       <c r="K21" s="3">
         <v>2092100</v>
@@ -1178,25 +1178,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>3265400</v>
+        <v>3320900</v>
       </c>
       <c r="E23" s="3">
-        <v>3253100</v>
+        <v>3308400</v>
       </c>
       <c r="F23" s="3">
-        <v>3263500</v>
+        <v>3319000</v>
       </c>
       <c r="G23" s="3">
-        <v>3257600</v>
+        <v>3313000</v>
       </c>
       <c r="H23" s="3">
-        <v>2950300</v>
+        <v>3000500</v>
       </c>
       <c r="I23" s="3">
-        <v>2831300</v>
+        <v>2879400</v>
       </c>
       <c r="J23" s="3">
-        <v>1877600</v>
+        <v>1909500</v>
       </c>
       <c r="K23" s="3">
         <v>1694700</v>
@@ -1213,25 +1213,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>972400</v>
+        <v>989000</v>
       </c>
       <c r="E24" s="3">
-        <v>935600</v>
+        <v>951500</v>
       </c>
       <c r="F24" s="3">
-        <v>931700</v>
+        <v>947500</v>
       </c>
       <c r="G24" s="3">
-        <v>970500</v>
+        <v>987000</v>
       </c>
       <c r="H24" s="3">
-        <v>861200</v>
+        <v>875800</v>
       </c>
       <c r="I24" s="3">
-        <v>922000</v>
+        <v>937700</v>
       </c>
       <c r="J24" s="3">
-        <v>557700</v>
+        <v>567200</v>
       </c>
       <c r="K24" s="3">
         <v>634000</v>
@@ -1283,25 +1283,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>2293000</v>
+        <v>2332000</v>
       </c>
       <c r="E26" s="3">
-        <v>2317600</v>
+        <v>2357000</v>
       </c>
       <c r="F26" s="3">
-        <v>2331800</v>
+        <v>2371400</v>
       </c>
       <c r="G26" s="3">
-        <v>2287100</v>
+        <v>2326000</v>
       </c>
       <c r="H26" s="3">
-        <v>2089200</v>
+        <v>2124700</v>
       </c>
       <c r="I26" s="3">
-        <v>1909300</v>
+        <v>1941800</v>
       </c>
       <c r="J26" s="3">
-        <v>1319900</v>
+        <v>1342300</v>
       </c>
       <c r="K26" s="3">
         <v>1060600</v>
@@ -1318,25 +1318,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>2283900</v>
+        <v>2322700</v>
       </c>
       <c r="E27" s="3">
-        <v>2308500</v>
+        <v>2347700</v>
       </c>
       <c r="F27" s="3">
-        <v>2331100</v>
+        <v>2370800</v>
       </c>
       <c r="G27" s="3">
-        <v>2287100</v>
+        <v>2326000</v>
       </c>
       <c r="H27" s="3">
-        <v>2088500</v>
+        <v>2124000</v>
       </c>
       <c r="I27" s="3">
-        <v>1909300</v>
+        <v>1941800</v>
       </c>
       <c r="J27" s="3">
-        <v>1319900</v>
+        <v>1342300</v>
       </c>
       <c r="K27" s="3">
         <v>1060000</v>
@@ -1394,19 +1394,19 @@
         <v>0</v>
       </c>
       <c r="F29" s="3">
-        <v>-9100</v>
+        <v>-9200</v>
       </c>
       <c r="G29" s="3">
-        <v>-3200</v>
+        <v>-3300</v>
       </c>
       <c r="H29" s="3">
-        <v>-5800</v>
+        <v>-5900</v>
       </c>
       <c r="I29" s="3">
-        <v>-5200</v>
+        <v>-5300</v>
       </c>
       <c r="J29" s="3">
-        <v>-5200</v>
+        <v>-5300</v>
       </c>
       <c r="K29" s="3">
         <v>-58300</v>
@@ -1493,25 +1493,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>1890500</v>
+        <v>1922700</v>
       </c>
       <c r="E32" s="3">
-        <v>2160300</v>
+        <v>2197100</v>
       </c>
       <c r="F32" s="3">
-        <v>1732700</v>
+        <v>1762100</v>
       </c>
       <c r="G32" s="3">
-        <v>1519800</v>
+        <v>1545600</v>
       </c>
       <c r="H32" s="3">
-        <v>1741100</v>
+        <v>1770700</v>
       </c>
       <c r="I32" s="3">
-        <v>2006300</v>
+        <v>2040500</v>
       </c>
       <c r="J32" s="3">
-        <v>1851100</v>
+        <v>1882500</v>
       </c>
       <c r="K32" s="3">
         <v>1902100</v>
@@ -1528,25 +1528,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>2283900</v>
+        <v>2322700</v>
       </c>
       <c r="E33" s="3">
-        <v>2308500</v>
+        <v>2347700</v>
       </c>
       <c r="F33" s="3">
-        <v>2322100</v>
+        <v>2361600</v>
       </c>
       <c r="G33" s="3">
-        <v>2283900</v>
+        <v>2322700</v>
       </c>
       <c r="H33" s="3">
-        <v>2082700</v>
+        <v>2118100</v>
       </c>
       <c r="I33" s="3">
-        <v>1904100</v>
+        <v>1936500</v>
       </c>
       <c r="J33" s="3">
-        <v>1314700</v>
+        <v>1337100</v>
       </c>
       <c r="K33" s="3">
         <v>1001600</v>
@@ -1598,25 +1598,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>2283900</v>
+        <v>2322700</v>
       </c>
       <c r="E35" s="3">
-        <v>2308500</v>
+        <v>2347700</v>
       </c>
       <c r="F35" s="3">
-        <v>2322100</v>
+        <v>2361600</v>
       </c>
       <c r="G35" s="3">
-        <v>2283900</v>
+        <v>2322700</v>
       </c>
       <c r="H35" s="3">
-        <v>2082700</v>
+        <v>2118100</v>
       </c>
       <c r="I35" s="3">
-        <v>1904100</v>
+        <v>1936500</v>
       </c>
       <c r="J35" s="3">
-        <v>1314700</v>
+        <v>1337100</v>
       </c>
       <c r="K35" s="3">
         <v>1001600</v>
@@ -1703,25 +1703,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>118854500</v>
+        <v>120875300</v>
       </c>
       <c r="E41" s="3">
-        <v>143470300</v>
+        <v>145909500</v>
       </c>
       <c r="F41" s="3">
-        <v>115678400</v>
+        <v>117645100</v>
       </c>
       <c r="G41" s="3">
-        <v>117002800</v>
+        <v>118992100</v>
       </c>
       <c r="H41" s="3">
-        <v>106639200</v>
+        <v>108452200</v>
       </c>
       <c r="I41" s="3">
-        <v>90762500</v>
+        <v>92305600</v>
       </c>
       <c r="J41" s="3">
-        <v>78596900</v>
+        <v>79933200</v>
       </c>
       <c r="K41" s="3">
         <v>101864800</v>
@@ -1738,25 +1738,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>68561300</v>
+        <v>69726900</v>
       </c>
       <c r="E42" s="3">
-        <v>61122100</v>
+        <v>62161300</v>
       </c>
       <c r="F42" s="3">
-        <v>89357800</v>
+        <v>90877000</v>
       </c>
       <c r="G42" s="3">
-        <v>61746400</v>
+        <v>62796200</v>
       </c>
       <c r="H42" s="3">
-        <v>59905700</v>
+        <v>60924200</v>
       </c>
       <c r="I42" s="3">
-        <v>105497200</v>
+        <v>107290800</v>
       </c>
       <c r="J42" s="3">
-        <v>129757100</v>
+        <v>131963200</v>
       </c>
       <c r="K42" s="3">
         <v>155272400</v>
@@ -1913,25 +1913,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1519800</v>
+        <v>1545600</v>
       </c>
       <c r="E47" s="3">
-        <v>1457700</v>
+        <v>1482500</v>
       </c>
       <c r="F47" s="3">
-        <v>1411100</v>
+        <v>1435100</v>
       </c>
       <c r="G47" s="3">
-        <v>1305600</v>
+        <v>1327800</v>
       </c>
       <c r="H47" s="3">
-        <v>1275900</v>
+        <v>1297600</v>
       </c>
       <c r="I47" s="3">
-        <v>1199500</v>
+        <v>1219900</v>
       </c>
       <c r="J47" s="3">
-        <v>1400100</v>
+        <v>1423900</v>
       </c>
       <c r="K47" s="3">
         <v>1499500</v>
@@ -1948,25 +1948,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1328300</v>
+        <v>1350900</v>
       </c>
       <c r="E48" s="3">
-        <v>1481000</v>
+        <v>1506200</v>
       </c>
       <c r="F48" s="3">
-        <v>1572900</v>
+        <v>1599600</v>
       </c>
       <c r="G48" s="3">
-        <v>1748200</v>
+        <v>1777900</v>
       </c>
       <c r="H48" s="3">
-        <v>1768900</v>
+        <v>1799000</v>
       </c>
       <c r="I48" s="3">
-        <v>1806400</v>
+        <v>1837100</v>
       </c>
       <c r="J48" s="3">
-        <v>1949400</v>
+        <v>1982600</v>
       </c>
       <c r="K48" s="3">
         <v>2081700</v>
@@ -1983,25 +1983,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2625500</v>
+        <v>2670200</v>
       </c>
       <c r="E49" s="3">
-        <v>2611900</v>
+        <v>2656300</v>
       </c>
       <c r="F49" s="3">
-        <v>2508400</v>
+        <v>2551100</v>
       </c>
       <c r="G49" s="3">
-        <v>2632000</v>
+        <v>2676700</v>
       </c>
       <c r="H49" s="3">
-        <v>2668200</v>
+        <v>2713600</v>
       </c>
       <c r="I49" s="3">
-        <v>2603500</v>
+        <v>2647800</v>
       </c>
       <c r="J49" s="3">
-        <v>2833200</v>
+        <v>2881400</v>
       </c>
       <c r="K49" s="3">
         <v>3213600</v>
@@ -2088,25 +2088,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2158400</v>
+        <v>2195100</v>
       </c>
       <c r="E52" s="3">
-        <v>1916400</v>
+        <v>1949000</v>
       </c>
       <c r="F52" s="3">
-        <v>2189400</v>
+        <v>2226700</v>
       </c>
       <c r="G52" s="3">
-        <v>1878200</v>
+        <v>1910200</v>
       </c>
       <c r="H52" s="3">
-        <v>1513300</v>
+        <v>1539100</v>
       </c>
       <c r="I52" s="3">
-        <v>1361900</v>
+        <v>1385100</v>
       </c>
       <c r="J52" s="3">
-        <v>1374200</v>
+        <v>1397600</v>
       </c>
       <c r="K52" s="3">
         <v>1177300</v>
@@ -2158,25 +2158,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>715336100</v>
+        <v>727498000</v>
       </c>
       <c r="E54" s="3">
-        <v>718946400</v>
+        <v>731169600</v>
       </c>
       <c r="F54" s="3">
-        <v>702466700</v>
+        <v>714409700</v>
       </c>
       <c r="G54" s="3">
-        <v>658232600</v>
+        <v>669423500</v>
       </c>
       <c r="H54" s="3">
-        <v>633320500</v>
+        <v>644087900</v>
       </c>
       <c r="I54" s="3">
-        <v>658865300</v>
+        <v>670067100</v>
       </c>
       <c r="J54" s="3">
-        <v>674359000</v>
+        <v>685824200</v>
       </c>
       <c r="K54" s="3">
         <v>745515800</v>
@@ -2223,25 +2223,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>9734100</v>
+        <v>9899600</v>
       </c>
       <c r="E57" s="3">
-        <v>8405200</v>
+        <v>8548100</v>
       </c>
       <c r="F57" s="3">
-        <v>6363200</v>
+        <v>6471400</v>
       </c>
       <c r="G57" s="3">
-        <v>6844600</v>
+        <v>6961000</v>
       </c>
       <c r="H57" s="3">
-        <v>5594600</v>
+        <v>5689700</v>
       </c>
       <c r="I57" s="3">
-        <v>5537000</v>
+        <v>5631200</v>
       </c>
       <c r="J57" s="3">
-        <v>5905800</v>
+        <v>6006200</v>
       </c>
       <c r="K57" s="3">
         <v>6830500</v>
@@ -2293,25 +2293,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>197300</v>
+        <v>200700</v>
       </c>
       <c r="E59" s="3">
-        <v>224500</v>
+        <v>228300</v>
       </c>
       <c r="F59" s="3">
-        <v>536400</v>
+        <v>545500</v>
       </c>
       <c r="G59" s="3">
-        <v>207000</v>
+        <v>210600</v>
       </c>
       <c r="H59" s="3">
-        <v>271100</v>
+        <v>275700</v>
       </c>
       <c r="I59" s="3">
-        <v>131300</v>
+        <v>133600</v>
       </c>
       <c r="J59" s="3">
-        <v>225800</v>
+        <v>229600</v>
       </c>
       <c r="K59" s="3">
         <v>158200</v>
@@ -2363,25 +2363,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>75061100</v>
+        <v>76337200</v>
       </c>
       <c r="E61" s="3">
-        <v>68683600</v>
+        <v>69851300</v>
       </c>
       <c r="F61" s="3">
-        <v>60645900</v>
+        <v>61677000</v>
       </c>
       <c r="G61" s="3">
-        <v>56435200</v>
+        <v>57394700</v>
       </c>
       <c r="H61" s="3">
-        <v>65381900</v>
+        <v>66493500</v>
       </c>
       <c r="I61" s="3">
-        <v>69632100</v>
+        <v>70815900</v>
       </c>
       <c r="J61" s="3">
-        <v>77425200</v>
+        <v>78741500</v>
       </c>
       <c r="K61" s="3">
         <v>90922800</v>
@@ -2398,25 +2398,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1532100</v>
+        <v>1558100</v>
       </c>
       <c r="E62" s="3">
-        <v>1530800</v>
+        <v>1556800</v>
       </c>
       <c r="F62" s="3">
-        <v>1620100</v>
+        <v>1647600</v>
       </c>
       <c r="G62" s="3">
-        <v>1895100</v>
+        <v>1927300</v>
       </c>
       <c r="H62" s="3">
-        <v>1867200</v>
+        <v>1899000</v>
       </c>
       <c r="I62" s="3">
-        <v>1999200</v>
+        <v>2033200</v>
       </c>
       <c r="J62" s="3">
-        <v>2106000</v>
+        <v>2141800</v>
       </c>
       <c r="K62" s="3">
         <v>2270300</v>
@@ -2538,25 +2538,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>670354100</v>
+        <v>681751200</v>
       </c>
       <c r="E66" s="3">
-        <v>674249100</v>
+        <v>685712300</v>
       </c>
       <c r="F66" s="3">
-        <v>659824800</v>
+        <v>671042900</v>
       </c>
       <c r="G66" s="3">
-        <v>618282300</v>
+        <v>628794000</v>
       </c>
       <c r="H66" s="3">
-        <v>592129200</v>
+        <v>602196300</v>
       </c>
       <c r="I66" s="3">
-        <v>618385100</v>
+        <v>628898600</v>
       </c>
       <c r="J66" s="3">
-        <v>634706400</v>
+        <v>645497300</v>
       </c>
       <c r="K66" s="3">
         <v>705733500</v>
@@ -2728,25 +2728,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>27328000</v>
+        <v>27792600</v>
       </c>
       <c r="E72" s="3">
-        <v>26582000</v>
+        <v>27033900</v>
       </c>
       <c r="F72" s="3">
-        <v>25732500</v>
+        <v>26170000</v>
       </c>
       <c r="G72" s="3">
-        <v>24657200</v>
+        <v>25076400</v>
       </c>
       <c r="H72" s="3">
-        <v>23620000</v>
+        <v>24021600</v>
       </c>
       <c r="I72" s="3">
-        <v>22802900</v>
+        <v>23190600</v>
       </c>
       <c r="J72" s="3">
-        <v>21556700</v>
+        <v>21923200</v>
       </c>
       <c r="K72" s="3">
         <v>20818900</v>
@@ -2868,25 +2868,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>44982000</v>
+        <v>45746800</v>
       </c>
       <c r="E76" s="3">
-        <v>44697300</v>
+        <v>45457300</v>
       </c>
       <c r="F76" s="3">
-        <v>42641800</v>
+        <v>43366800</v>
       </c>
       <c r="G76" s="3">
-        <v>39950300</v>
+        <v>40629500</v>
       </c>
       <c r="H76" s="3">
-        <v>41191300</v>
+        <v>41891600</v>
       </c>
       <c r="I76" s="3">
-        <v>40480200</v>
+        <v>41168400</v>
       </c>
       <c r="J76" s="3">
-        <v>39652700</v>
+        <v>40326800</v>
       </c>
       <c r="K76" s="3">
         <v>39782300</v>
@@ -2978,25 +2978,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>2283900</v>
+        <v>2322700</v>
       </c>
       <c r="E81" s="3">
-        <v>2308500</v>
+        <v>2347700</v>
       </c>
       <c r="F81" s="3">
-        <v>2322100</v>
+        <v>2361600</v>
       </c>
       <c r="G81" s="3">
-        <v>2283900</v>
+        <v>2322700</v>
       </c>
       <c r="H81" s="3">
-        <v>2082700</v>
+        <v>2118100</v>
       </c>
       <c r="I81" s="3">
-        <v>1904100</v>
+        <v>1936500</v>
       </c>
       <c r="J81" s="3">
-        <v>1314700</v>
+        <v>1337100</v>
       </c>
       <c r="K81" s="3">
         <v>1001600</v>
@@ -3028,25 +3028,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>292400</v>
+        <v>297400</v>
       </c>
       <c r="E83" s="3">
-        <v>304700</v>
+        <v>309900</v>
       </c>
       <c r="F83" s="3">
-        <v>322900</v>
+        <v>328300</v>
       </c>
       <c r="G83" s="3">
-        <v>329300</v>
+        <v>334900</v>
       </c>
       <c r="H83" s="3">
-        <v>339000</v>
+        <v>344800</v>
       </c>
       <c r="I83" s="3">
-        <v>364300</v>
+        <v>370500</v>
       </c>
       <c r="J83" s="3">
-        <v>503400</v>
+        <v>511900</v>
       </c>
       <c r="K83" s="3">
         <v>397400</v>
@@ -3238,25 +3238,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-21330900</v>
+        <v>-21693600</v>
       </c>
       <c r="E89" s="3">
-        <v>25528700</v>
+        <v>25962700</v>
       </c>
       <c r="F89" s="3">
-        <v>-8064900</v>
+        <v>-8202000</v>
       </c>
       <c r="G89" s="3">
-        <v>21118700</v>
+        <v>21477800</v>
       </c>
       <c r="H89" s="3">
-        <v>9058600</v>
+        <v>9212700</v>
       </c>
       <c r="I89" s="3">
-        <v>19294200</v>
+        <v>19622200</v>
       </c>
       <c r="J89" s="3">
-        <v>-1528900</v>
+        <v>-1554900</v>
       </c>
       <c r="K89" s="3">
         <v>35427700</v>
@@ -3393,25 +3393,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-1426600</v>
+        <v>-1450900</v>
       </c>
       <c r="E94" s="3">
-        <v>-5487200</v>
+        <v>-5580500</v>
       </c>
       <c r="F94" s="3">
-        <v>-1882800</v>
+        <v>-1914800</v>
       </c>
       <c r="G94" s="3">
-        <v>707200</v>
+        <v>719200</v>
       </c>
       <c r="H94" s="3">
-        <v>7214700</v>
+        <v>7337400</v>
       </c>
       <c r="I94" s="3">
-        <v>-577800</v>
+        <v>-587600</v>
       </c>
       <c r="J94" s="3">
-        <v>-8379300</v>
+        <v>-8521800</v>
       </c>
       <c r="K94" s="3">
         <v>963400</v>
@@ -3443,25 +3443,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-1553400</v>
+        <v>-1579900</v>
       </c>
       <c r="E96" s="3">
-        <v>-1280400</v>
+        <v>-1302200</v>
       </c>
       <c r="F96" s="3">
-        <v>-1158100</v>
+        <v>-1177800</v>
       </c>
       <c r="G96" s="3">
-        <v>-1290100</v>
+        <v>-1312100</v>
       </c>
       <c r="H96" s="3">
-        <v>-1264900</v>
+        <v>-1286400</v>
       </c>
       <c r="I96" s="3">
-        <v>-568700</v>
+        <v>-578400</v>
       </c>
       <c r="J96" s="3">
-        <v>-409600</v>
+        <v>-416500</v>
       </c>
       <c r="K96" s="3">
         <v>-1444400</v>
@@ -3583,25 +3583,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-3073300</v>
+        <v>-3125500</v>
       </c>
       <c r="E100" s="3">
-        <v>5910300</v>
+        <v>6010800</v>
       </c>
       <c r="F100" s="3">
-        <v>6306300</v>
+        <v>6413500</v>
       </c>
       <c r="G100" s="3">
-        <v>-7823500</v>
+        <v>-7956500</v>
       </c>
       <c r="H100" s="3">
-        <v>-1189200</v>
+        <v>-1209400</v>
       </c>
       <c r="I100" s="3">
-        <v>-5068600</v>
+        <v>-5154800</v>
       </c>
       <c r="J100" s="3">
-        <v>362300</v>
+        <v>368500</v>
       </c>
       <c r="K100" s="3">
         <v>-643100</v>
@@ -3618,25 +3618,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-467100</v>
+        <v>-475100</v>
       </c>
       <c r="E101" s="3">
-        <v>360400</v>
+        <v>366500</v>
       </c>
       <c r="F101" s="3">
-        <v>3691800</v>
+        <v>3754500</v>
       </c>
       <c r="G101" s="3">
-        <v>-3136700</v>
+        <v>-3190000</v>
       </c>
       <c r="H101" s="3">
-        <v>2255400</v>
+        <v>2293800</v>
       </c>
       <c r="I101" s="3">
-        <v>-2948400</v>
+        <v>-2998500</v>
       </c>
       <c r="J101" s="3">
-        <v>-5443900</v>
+        <v>-5536400</v>
       </c>
       <c r="K101" s="3">
         <v>4104400</v>
@@ -3653,25 +3653,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-26298000</v>
+        <v>-26745100</v>
       </c>
       <c r="E102" s="3">
-        <v>26312200</v>
+        <v>26759500</v>
       </c>
       <c r="F102" s="3">
-        <v>50500</v>
+        <v>51300</v>
       </c>
       <c r="G102" s="3">
-        <v>10865700</v>
+        <v>11050500</v>
       </c>
       <c r="H102" s="3">
-        <v>17339600</v>
+        <v>17634400</v>
       </c>
       <c r="I102" s="3">
-        <v>10699400</v>
+        <v>10881300</v>
       </c>
       <c r="J102" s="3">
-        <v>-22755000</v>
+        <v>-23141900</v>
       </c>
       <c r="K102" s="3">
         <v>39852300</v>

--- a/AAII_Financials/Quarterly/ANZGY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ANZGY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="92">
   <si>
     <t>ANZGY</t>
   </si>
@@ -656,97 +656,103 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:M102"/>
+  <dimension ref="A5:N102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="13" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45016</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44834</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44651</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44469</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44286</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44104</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43921</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>43738</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>17808100</v>
+        <v>19863100</v>
       </c>
       <c r="E8" s="3">
-        <v>15027400</v>
+        <v>18038100</v>
       </c>
       <c r="F8" s="3">
-        <v>9147500</v>
+        <v>15213000</v>
       </c>
       <c r="G8" s="3">
-        <v>6387200</v>
+        <v>9262900</v>
       </c>
       <c r="H8" s="3">
-        <v>6349700</v>
+        <v>6467800</v>
       </c>
       <c r="I8" s="3">
-        <v>6500400</v>
+        <v>6429800</v>
       </c>
       <c r="J8" s="3">
+        <v>6582400</v>
+      </c>
+      <c r="K8" s="3">
         <v>6991900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>8946500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>9955500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>10524200</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -780,8 +786,11 @@
       <c r="M9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -815,8 +824,11 @@
       <c r="M10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -830,8 +842,9 @@
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N11" s="3"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -865,8 +878,11 @@
       <c r="M12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -900,8 +916,11 @@
       <c r="M13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -935,43 +954,49 @@
       <c r="M14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-163800</v>
+        <v>-293800</v>
       </c>
       <c r="E15" s="3">
-        <v>-168400</v>
+        <v>-165200</v>
       </c>
       <c r="F15" s="3">
-        <v>-187500</v>
+        <v>-311200</v>
       </c>
       <c r="G15" s="3">
-        <v>-192800</v>
+        <v>-189900</v>
       </c>
       <c r="H15" s="3">
-        <v>-200000</v>
+        <v>-195200</v>
       </c>
       <c r="I15" s="3">
-        <v>-219800</v>
+        <v>-202600</v>
       </c>
       <c r="J15" s="3">
+        <v>-222500</v>
+      </c>
+      <c r="K15" s="3">
         <v>-340200</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>-221100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>-235300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>-222100</v>
       </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -982,78 +1007,85 @@
       <c r="K16" s="3"/>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-    </row>
-    <row r="17" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N16" s="3"/>
+    </row>
+    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>12564500</v>
+        <v>14646600</v>
       </c>
       <c r="E17" s="3">
-        <v>9521900</v>
+        <v>12730300</v>
       </c>
       <c r="F17" s="3">
-        <v>4066400</v>
+        <v>9638000</v>
       </c>
       <c r="G17" s="3">
-        <v>1528500</v>
+        <v>4117700</v>
       </c>
       <c r="H17" s="3">
-        <v>1578500</v>
+        <v>1547800</v>
       </c>
       <c r="I17" s="3">
-        <v>1580500</v>
+        <v>1598500</v>
       </c>
       <c r="J17" s="3">
+        <v>1600500</v>
+      </c>
+      <c r="K17" s="3">
         <v>3199900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>5349800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>5581100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>5972500</v>
       </c>
     </row>
-    <row r="18" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>5243600</v>
+        <v>5216500</v>
       </c>
       <c r="E18" s="3">
-        <v>5505500</v>
+        <v>5307700</v>
       </c>
       <c r="F18" s="3">
-        <v>5081100</v>
+        <v>5574900</v>
       </c>
       <c r="G18" s="3">
-        <v>4858700</v>
+        <v>5145200</v>
       </c>
       <c r="H18" s="3">
-        <v>4771200</v>
+        <v>4920000</v>
       </c>
       <c r="I18" s="3">
-        <v>4919900</v>
+        <v>4831300</v>
       </c>
       <c r="J18" s="3">
+        <v>4981900</v>
+      </c>
+      <c r="K18" s="3">
         <v>3792100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>3596800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>4374400</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>4551700</v>
       </c>
     </row>
-    <row r="19" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1067,78 +1099,85 @@
       <c r="K19" s="3"/>
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
-    </row>
-    <row r="20" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N19" s="3"/>
+    </row>
+    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-1922700</v>
+        <v>-1978200</v>
       </c>
       <c r="E20" s="3">
-        <v>-2197100</v>
+        <v>-1932300</v>
       </c>
       <c r="F20" s="3">
-        <v>-1762100</v>
+        <v>-2229400</v>
       </c>
       <c r="G20" s="3">
-        <v>-1545600</v>
+        <v>-1784400</v>
       </c>
       <c r="H20" s="3">
-        <v>-1770700</v>
+        <v>-1565100</v>
       </c>
       <c r="I20" s="3">
-        <v>-2040500</v>
+        <v>-1793000</v>
       </c>
       <c r="J20" s="3">
+        <v>-2066200</v>
+      </c>
+      <c r="K20" s="3">
         <v>-1882500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1902100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1485400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1562500</v>
       </c>
     </row>
-    <row r="21" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>3618300</v>
+        <v>3534700</v>
       </c>
       <c r="E21" s="3">
-        <v>3618300</v>
+        <v>3676600</v>
       </c>
       <c r="F21" s="3">
-        <v>3647300</v>
+        <v>3659300</v>
       </c>
       <c r="G21" s="3">
-        <v>3648000</v>
+        <v>3693300</v>
       </c>
       <c r="H21" s="3">
-        <v>3345300</v>
+        <v>3694000</v>
       </c>
       <c r="I21" s="3">
-        <v>3249900</v>
+        <v>3387500</v>
       </c>
       <c r="J21" s="3">
+        <v>3290900</v>
+      </c>
+      <c r="K21" s="3">
         <v>2421400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>2092100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>3181000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>3271300</v>
       </c>
     </row>
-    <row r="22" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1172,78 +1211,87 @@
       <c r="M22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>3320900</v>
+        <v>3238200</v>
       </c>
       <c r="E23" s="3">
-        <v>3308400</v>
+        <v>3375500</v>
       </c>
       <c r="F23" s="3">
-        <v>3319000</v>
+        <v>3345500</v>
       </c>
       <c r="G23" s="3">
-        <v>3313000</v>
+        <v>3360800</v>
       </c>
       <c r="H23" s="3">
-        <v>3000500</v>
+        <v>3354800</v>
       </c>
       <c r="I23" s="3">
-        <v>2879400</v>
+        <v>3038300</v>
       </c>
       <c r="J23" s="3">
+        <v>2915700</v>
+      </c>
+      <c r="K23" s="3">
         <v>1909500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>1694700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>2889100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>2989200</v>
       </c>
     </row>
-    <row r="24" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>989000</v>
+        <v>958800</v>
       </c>
       <c r="E24" s="3">
-        <v>951500</v>
+        <v>1000100</v>
       </c>
       <c r="F24" s="3">
-        <v>947500</v>
+        <v>967500</v>
       </c>
       <c r="G24" s="3">
-        <v>987000</v>
+        <v>959500</v>
       </c>
       <c r="H24" s="3">
-        <v>875800</v>
+        <v>999500</v>
       </c>
       <c r="I24" s="3">
-        <v>937700</v>
+        <v>886800</v>
       </c>
       <c r="J24" s="3">
+        <v>949500</v>
+      </c>
+      <c r="K24" s="3">
         <v>567200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>634000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>873200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>846200</v>
       </c>
     </row>
-    <row r="25" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1277,78 +1325,87 @@
       <c r="M25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>2332000</v>
+        <v>2279400</v>
       </c>
       <c r="E26" s="3">
-        <v>2357000</v>
+        <v>2375400</v>
       </c>
       <c r="F26" s="3">
-        <v>2371400</v>
+        <v>2378000</v>
       </c>
       <c r="G26" s="3">
-        <v>2326000</v>
+        <v>2401300</v>
       </c>
       <c r="H26" s="3">
-        <v>2124700</v>
+        <v>2355400</v>
       </c>
       <c r="I26" s="3">
-        <v>1941800</v>
+        <v>2151500</v>
       </c>
       <c r="J26" s="3">
+        <v>1966300</v>
+      </c>
+      <c r="K26" s="3">
         <v>1342300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>1060600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2015900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2143100</v>
       </c>
     </row>
-    <row r="27" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>2322700</v>
+        <v>2270100</v>
       </c>
       <c r="E27" s="3">
-        <v>2347700</v>
+        <v>2366000</v>
       </c>
       <c r="F27" s="3">
-        <v>2370800</v>
+        <v>2368700</v>
       </c>
       <c r="G27" s="3">
-        <v>2326000</v>
+        <v>2400700</v>
       </c>
       <c r="H27" s="3">
-        <v>2124000</v>
+        <v>2355400</v>
       </c>
       <c r="I27" s="3">
-        <v>1941800</v>
+        <v>2150800</v>
       </c>
       <c r="J27" s="3">
+        <v>1966300</v>
+      </c>
+      <c r="K27" s="3">
         <v>1342300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>1060000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2011900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2137100</v>
       </c>
     </row>
-    <row r="28" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1382,43 +1439,49 @@
       <c r="M28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3">
-        <v>0</v>
+      <c r="D29" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="E29" s="3">
         <v>0</v>
       </c>
       <c r="F29" s="3">
-        <v>-9200</v>
+        <v>0</v>
       </c>
       <c r="G29" s="3">
+        <v>-9300</v>
+      </c>
+      <c r="H29" s="3">
         <v>-3300</v>
       </c>
-      <c r="H29" s="3">
-        <v>-5900</v>
-      </c>
       <c r="I29" s="3">
-        <v>-5300</v>
+        <v>-6000</v>
       </c>
       <c r="J29" s="3">
         <v>-5300</v>
       </c>
       <c r="K29" s="3">
+        <v>-5300</v>
+      </c>
+      <c r="L29" s="3">
         <v>-58300</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-179900</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-46100</v>
       </c>
     </row>
-    <row r="30" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1452,8 +1515,11 @@
       <c r="M30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1487,78 +1553,87 @@
       <c r="M31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>1922700</v>
+        <v>1978200</v>
       </c>
       <c r="E32" s="3">
-        <v>2197100</v>
+        <v>1932300</v>
       </c>
       <c r="F32" s="3">
-        <v>1762100</v>
+        <v>2229400</v>
       </c>
       <c r="G32" s="3">
-        <v>1545600</v>
+        <v>1784400</v>
       </c>
       <c r="H32" s="3">
-        <v>1770700</v>
+        <v>1565100</v>
       </c>
       <c r="I32" s="3">
-        <v>2040500</v>
+        <v>1793000</v>
       </c>
       <c r="J32" s="3">
+        <v>2066200</v>
+      </c>
+      <c r="K32" s="3">
         <v>1882500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1902100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1485400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1562500</v>
       </c>
     </row>
-    <row r="33" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>2322700</v>
+        <v>2270100</v>
       </c>
       <c r="E33" s="3">
-        <v>2347700</v>
+        <v>2366000</v>
       </c>
       <c r="F33" s="3">
-        <v>2361600</v>
+        <v>2368700</v>
       </c>
       <c r="G33" s="3">
-        <v>2322700</v>
+        <v>2391400</v>
       </c>
       <c r="H33" s="3">
-        <v>2118100</v>
+        <v>2352000</v>
       </c>
       <c r="I33" s="3">
-        <v>1936500</v>
+        <v>2144800</v>
       </c>
       <c r="J33" s="3">
+        <v>1960900</v>
+      </c>
+      <c r="K33" s="3">
         <v>1337100</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>1001600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1832000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2091000</v>
       </c>
     </row>
-    <row r="34" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1592,83 +1667,92 @@
       <c r="M34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>2322700</v>
+        <v>2270100</v>
       </c>
       <c r="E35" s="3">
-        <v>2347700</v>
+        <v>2366000</v>
       </c>
       <c r="F35" s="3">
-        <v>2361600</v>
+        <v>2368700</v>
       </c>
       <c r="G35" s="3">
-        <v>2322700</v>
+        <v>2391400</v>
       </c>
       <c r="H35" s="3">
-        <v>2118100</v>
+        <v>2352000</v>
       </c>
       <c r="I35" s="3">
-        <v>1936500</v>
+        <v>2144800</v>
       </c>
       <c r="J35" s="3">
+        <v>1960900</v>
+      </c>
+      <c r="K35" s="3">
         <v>1337100</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>1001600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1832000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2091000</v>
       </c>
     </row>
-    <row r="37" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45016</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44834</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44651</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44469</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44286</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44104</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43921</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>43738</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="39" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1682,8 +1766,9 @@
       <c r="K39" s="3"/>
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
-    </row>
-    <row r="40" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N39" s="3"/>
+    </row>
+    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1697,78 +1782,85 @@
       <c r="K40" s="3"/>
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
-    </row>
-    <row r="41" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N40" s="3"/>
+    </row>
+    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>120875300</v>
+        <v>98355900</v>
       </c>
       <c r="E41" s="3">
-        <v>145909500</v>
+        <v>122400000</v>
       </c>
       <c r="F41" s="3">
-        <v>117645100</v>
+        <v>147750000</v>
       </c>
       <c r="G41" s="3">
-        <v>118992100</v>
+        <v>119129100</v>
       </c>
       <c r="H41" s="3">
-        <v>108452200</v>
+        <v>120493000</v>
       </c>
       <c r="I41" s="3">
-        <v>92305600</v>
+        <v>109820200</v>
       </c>
       <c r="J41" s="3">
+        <v>93469900</v>
+      </c>
+      <c r="K41" s="3">
         <v>79933200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>101864800</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>61620500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>70159800</v>
       </c>
     </row>
-    <row r="42" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>69726900</v>
+        <v>65406700</v>
       </c>
       <c r="E42" s="3">
-        <v>62161300</v>
+        <v>70606500</v>
       </c>
       <c r="F42" s="3">
-        <v>90877000</v>
+        <v>62945400</v>
       </c>
       <c r="G42" s="3">
-        <v>62796200</v>
+        <v>92023400</v>
       </c>
       <c r="H42" s="3">
-        <v>60924200</v>
+        <v>63588300</v>
       </c>
       <c r="I42" s="3">
-        <v>107290800</v>
+        <v>61692700</v>
       </c>
       <c r="J42" s="3">
+        <v>108644200</v>
+      </c>
+      <c r="K42" s="3">
         <v>131963200</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>155272400</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>117856900</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>88366600</v>
       </c>
     </row>
-    <row r="43" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
@@ -1802,8 +1894,11 @@
       <c r="M43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -1837,8 +1932,11 @@
       <c r="M44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -1872,8 +1970,11 @@
       <c r="M45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -1907,113 +2008,125 @@
       <c r="M46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>1545600</v>
+        <v>945500</v>
       </c>
       <c r="E47" s="3">
-        <v>1482500</v>
+        <v>1565100</v>
       </c>
       <c r="F47" s="3">
-        <v>1435100</v>
+        <v>1501200</v>
       </c>
       <c r="G47" s="3">
-        <v>1327800</v>
+        <v>1453200</v>
       </c>
       <c r="H47" s="3">
-        <v>1297600</v>
+        <v>1344600</v>
       </c>
       <c r="I47" s="3">
-        <v>1219900</v>
+        <v>1313900</v>
       </c>
       <c r="J47" s="3">
+        <v>1235300</v>
+      </c>
+      <c r="K47" s="3">
         <v>1423900</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1499500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>1948700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>1803700</v>
       </c>
     </row>
-    <row r="48" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1350900</v>
+        <v>1335900</v>
       </c>
       <c r="E48" s="3">
-        <v>1506200</v>
+        <v>1367900</v>
       </c>
       <c r="F48" s="3">
-        <v>1599600</v>
+        <v>1525200</v>
       </c>
       <c r="G48" s="3">
-        <v>1777900</v>
+        <v>1619800</v>
       </c>
       <c r="H48" s="3">
-        <v>1799000</v>
+        <v>1800300</v>
       </c>
       <c r="I48" s="3">
-        <v>1837100</v>
+        <v>1821700</v>
       </c>
       <c r="J48" s="3">
+        <v>1860300</v>
+      </c>
+      <c r="K48" s="3">
         <v>1982600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2081700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1267900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1227700</v>
       </c>
     </row>
-    <row r="49" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2670200</v>
+        <v>2663900</v>
       </c>
       <c r="E49" s="3">
-        <v>2656300</v>
+        <v>2703800</v>
       </c>
       <c r="F49" s="3">
-        <v>2551100</v>
+        <v>2689900</v>
       </c>
       <c r="G49" s="3">
-        <v>2676700</v>
+        <v>2583200</v>
       </c>
       <c r="H49" s="3">
-        <v>2713600</v>
+        <v>2710500</v>
       </c>
       <c r="I49" s="3">
-        <v>2647800</v>
+        <v>2747800</v>
       </c>
       <c r="J49" s="3">
+        <v>2681200</v>
+      </c>
+      <c r="K49" s="3">
         <v>2881400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3213600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3203400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3306200</v>
       </c>
     </row>
-    <row r="50" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2047,8 +2160,11 @@
       <c r="M50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2082,43 +2198,49 @@
       <c r="M51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2195100</v>
+        <v>2098200</v>
       </c>
       <c r="E52" s="3">
-        <v>1949000</v>
+        <v>2230800</v>
       </c>
       <c r="F52" s="3">
-        <v>2226700</v>
+        <v>1981600</v>
       </c>
       <c r="G52" s="3">
-        <v>1910200</v>
+        <v>2254800</v>
       </c>
       <c r="H52" s="3">
-        <v>1539100</v>
+        <v>1934300</v>
       </c>
       <c r="I52" s="3">
-        <v>1385100</v>
+        <v>1558500</v>
       </c>
       <c r="J52" s="3">
+        <v>1402600</v>
+      </c>
+      <c r="K52" s="3">
         <v>1397600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>1177300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>2100200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>29454000</v>
       </c>
     </row>
-    <row r="53" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2152,43 +2274,49 @@
       <c r="M53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>727498000</v>
+        <v>726066400</v>
       </c>
       <c r="E54" s="3">
-        <v>731169600</v>
+        <v>736689900</v>
       </c>
       <c r="F54" s="3">
-        <v>714409700</v>
+        <v>740417200</v>
       </c>
       <c r="G54" s="3">
-        <v>669423500</v>
+        <v>723421200</v>
       </c>
       <c r="H54" s="3">
-        <v>644087900</v>
+        <v>677867600</v>
       </c>
       <c r="I54" s="3">
-        <v>670067100</v>
+        <v>652212400</v>
       </c>
       <c r="J54" s="3">
+        <v>678519300</v>
+      </c>
+      <c r="K54" s="3">
         <v>685824200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>745515800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>646569300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>645997900</v>
       </c>
     </row>
-    <row r="55" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2202,8 +2330,9 @@
       <c r="K55" s="3"/>
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
-    </row>
-    <row r="56" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N55" s="3"/>
+    </row>
+    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2217,43 +2346,47 @@
       <c r="K56" s="3"/>
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
-    </row>
-    <row r="57" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N56" s="3"/>
+    </row>
+    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>9899600</v>
+        <v>11389700</v>
       </c>
       <c r="E57" s="3">
-        <v>8548100</v>
+        <v>10059100</v>
       </c>
       <c r="F57" s="3">
-        <v>6471400</v>
+        <v>8699900</v>
       </c>
       <c r="G57" s="3">
-        <v>6961000</v>
+        <v>6553100</v>
       </c>
       <c r="H57" s="3">
-        <v>5689700</v>
+        <v>7048800</v>
       </c>
       <c r="I57" s="3">
-        <v>5631200</v>
+        <v>5761500</v>
       </c>
       <c r="J57" s="3">
+        <v>5702200</v>
+      </c>
+      <c r="K57" s="3">
         <v>6006200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>6830500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>5250900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5035400</v>
       </c>
     </row>
-    <row r="58" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -2287,43 +2420,49 @@
       <c r="M58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>200700</v>
+        <v>133900</v>
       </c>
       <c r="E59" s="3">
-        <v>228300</v>
+        <v>203200</v>
       </c>
       <c r="F59" s="3">
-        <v>545500</v>
+        <v>231200</v>
       </c>
       <c r="G59" s="3">
-        <v>210600</v>
+        <v>552400</v>
       </c>
       <c r="H59" s="3">
-        <v>275700</v>
+        <v>213200</v>
       </c>
       <c r="I59" s="3">
-        <v>133600</v>
+        <v>279200</v>
       </c>
       <c r="J59" s="3">
+        <v>135300</v>
+      </c>
+      <c r="K59" s="3">
         <v>229600</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>158200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>171300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>104800</v>
       </c>
     </row>
-    <row r="60" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -2357,78 +2496,87 @@
       <c r="M60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>76337200</v>
+        <v>84692700</v>
       </c>
       <c r="E61" s="3">
-        <v>69851300</v>
+        <v>77300100</v>
       </c>
       <c r="F61" s="3">
-        <v>61677000</v>
+        <v>70732400</v>
       </c>
       <c r="G61" s="3">
-        <v>57394700</v>
+        <v>62455000</v>
       </c>
       <c r="H61" s="3">
-        <v>66493500</v>
+        <v>58118700</v>
       </c>
       <c r="I61" s="3">
-        <v>70815900</v>
+        <v>67332300</v>
       </c>
       <c r="J61" s="3">
+        <v>71709200</v>
+      </c>
+      <c r="K61" s="3">
         <v>78741500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>90922800</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>85466400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>85467000</v>
       </c>
     </row>
-    <row r="62" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1558100</v>
+        <v>1546500</v>
       </c>
       <c r="E62" s="3">
-        <v>1556800</v>
+        <v>1577800</v>
       </c>
       <c r="F62" s="3">
-        <v>1647600</v>
+        <v>1576500</v>
       </c>
       <c r="G62" s="3">
-        <v>1927300</v>
+        <v>1668400</v>
       </c>
       <c r="H62" s="3">
-        <v>1899000</v>
+        <v>1951600</v>
       </c>
       <c r="I62" s="3">
-        <v>2033200</v>
+        <v>1922900</v>
       </c>
       <c r="J62" s="3">
+        <v>2058900</v>
+      </c>
+      <c r="K62" s="3">
         <v>2141800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>2270300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>3295000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>32638300</v>
       </c>
     </row>
-    <row r="63" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2462,8 +2610,11 @@
       <c r="M63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2497,8 +2648,11 @@
       <c r="M64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2532,43 +2686,49 @@
       <c r="M65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>681751200</v>
+        <v>679221600</v>
       </c>
       <c r="E66" s="3">
-        <v>685712300</v>
+        <v>690385400</v>
       </c>
       <c r="F66" s="3">
-        <v>671042900</v>
+        <v>694405900</v>
       </c>
       <c r="G66" s="3">
-        <v>628794000</v>
+        <v>679507400</v>
       </c>
       <c r="H66" s="3">
-        <v>602196300</v>
+        <v>636725600</v>
       </c>
       <c r="I66" s="3">
-        <v>628898600</v>
+        <v>609792400</v>
       </c>
       <c r="J66" s="3">
+        <v>636831500</v>
+      </c>
+      <c r="K66" s="3">
         <v>645497300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>705733500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>606513300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>606575900</v>
       </c>
     </row>
-    <row r="67" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2582,8 +2742,9 @@
       <c r="K67" s="3"/>
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
-    </row>
-    <row r="68" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N67" s="3"/>
+    </row>
+    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2617,8 +2778,11 @@
       <c r="M68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2652,8 +2816,11 @@
       <c r="M69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2687,8 +2854,11 @@
       <c r="M70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2722,43 +2892,49 @@
       <c r="M71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>27792600</v>
+        <v>28511600</v>
       </c>
       <c r="E72" s="3">
-        <v>27033900</v>
+        <v>28123900</v>
       </c>
       <c r="F72" s="3">
-        <v>26170000</v>
+        <v>27355600</v>
       </c>
       <c r="G72" s="3">
-        <v>25076400</v>
+        <v>26500100</v>
       </c>
       <c r="H72" s="3">
-        <v>24021600</v>
+        <v>25392700</v>
       </c>
       <c r="I72" s="3">
-        <v>23190600</v>
+        <v>24324600</v>
       </c>
       <c r="J72" s="3">
+        <v>23483100</v>
+      </c>
+      <c r="K72" s="3">
         <v>21923200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>20818900</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>21569700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>21162500</v>
       </c>
     </row>
-    <row r="73" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2792,8 +2968,11 @@
       <c r="M73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -2827,8 +3006,11 @@
       <c r="M74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -2862,43 +3044,49 @@
       <c r="M75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>45746800</v>
+        <v>46844900</v>
       </c>
       <c r="E76" s="3">
-        <v>45457300</v>
+        <v>46304500</v>
       </c>
       <c r="F76" s="3">
-        <v>43366800</v>
+        <v>46011300</v>
       </c>
       <c r="G76" s="3">
-        <v>40629500</v>
+        <v>43913800</v>
       </c>
       <c r="H76" s="3">
-        <v>41891600</v>
+        <v>41142000</v>
       </c>
       <c r="I76" s="3">
-        <v>41168400</v>
+        <v>42420000</v>
       </c>
       <c r="J76" s="3">
+        <v>41687700</v>
+      </c>
+      <c r="K76" s="3">
         <v>40326800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>39782300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>40056000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>39422000</v>
       </c>
     </row>
-    <row r="77" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -2932,83 +3120,92 @@
       <c r="M77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:13" x14ac:dyDescent="0.2">
+      <c r="N77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:13" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45016</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44834</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44651</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44469</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44286</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44104</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43921</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>43738</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="81" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>2322700</v>
+        <v>2270100</v>
       </c>
       <c r="E81" s="3">
-        <v>2347700</v>
+        <v>2366000</v>
       </c>
       <c r="F81" s="3">
-        <v>2361600</v>
+        <v>2368700</v>
       </c>
       <c r="G81" s="3">
-        <v>2322700</v>
+        <v>2391400</v>
       </c>
       <c r="H81" s="3">
-        <v>2118100</v>
+        <v>2352000</v>
       </c>
       <c r="I81" s="3">
-        <v>1936500</v>
+        <v>2144800</v>
       </c>
       <c r="J81" s="3">
+        <v>1960900</v>
+      </c>
+      <c r="K81" s="3">
         <v>1337100</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>1001600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1832000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2091000</v>
       </c>
     </row>
-    <row r="82" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3022,43 +3219,47 @@
       <c r="K82" s="3"/>
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
-    </row>
-    <row r="83" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N82" s="3"/>
+    </row>
+    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>297400</v>
+        <v>296500</v>
       </c>
       <c r="E83" s="3">
-        <v>309900</v>
+        <v>301200</v>
       </c>
       <c r="F83" s="3">
-        <v>328300</v>
+        <v>313800</v>
       </c>
       <c r="G83" s="3">
-        <v>334900</v>
+        <v>332500</v>
       </c>
       <c r="H83" s="3">
-        <v>344800</v>
+        <v>339100</v>
       </c>
       <c r="I83" s="3">
-        <v>370500</v>
+        <v>349100</v>
       </c>
       <c r="J83" s="3">
+        <v>375100</v>
+      </c>
+      <c r="K83" s="3">
         <v>511900</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>397400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>291900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>282100</v>
       </c>
     </row>
-    <row r="84" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3092,8 +3293,11 @@
       <c r="M84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3127,8 +3331,11 @@
       <c r="M85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3162,8 +3369,11 @@
       <c r="M86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3197,8 +3407,11 @@
       <c r="M87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3232,43 +3445,49 @@
       <c r="M88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-21693600</v>
+        <v>-10392300</v>
       </c>
       <c r="E89" s="3">
-        <v>25962700</v>
+        <v>-21967200</v>
       </c>
       <c r="F89" s="3">
-        <v>-8202000</v>
+        <v>26290200</v>
       </c>
       <c r="G89" s="3">
-        <v>21477800</v>
+        <v>-8305400</v>
       </c>
       <c r="H89" s="3">
-        <v>9212700</v>
+        <v>21748700</v>
       </c>
       <c r="I89" s="3">
-        <v>19622200</v>
+        <v>9328900</v>
       </c>
       <c r="J89" s="3">
+        <v>19869700</v>
+      </c>
+      <c r="K89" s="3">
         <v>-1554900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>35427700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-7995600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>4997200</v>
       </c>
     </row>
-    <row r="90" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3282,13 +3501,14 @@
       <c r="K90" s="3"/>
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
-    </row>
-    <row r="91" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N90" s="3"/>
+    </row>
+    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-117000</v>
+        <v>0</v>
       </c>
       <c r="E91" s="3">
         <v>0</v>
@@ -3317,8 +3537,11 @@
       <c r="M91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3352,8 +3575,11 @@
       <c r="M92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3387,43 +3613,49 @@
       <c r="M93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-1450900</v>
+        <v>-13783700</v>
       </c>
       <c r="E94" s="3">
-        <v>-5580500</v>
+        <v>-1469200</v>
       </c>
       <c r="F94" s="3">
-        <v>-1914800</v>
+        <v>-5650900</v>
       </c>
       <c r="G94" s="3">
-        <v>719200</v>
+        <v>-1938900</v>
       </c>
       <c r="H94" s="3">
-        <v>7337400</v>
+        <v>728300</v>
       </c>
       <c r="I94" s="3">
-        <v>-587600</v>
+        <v>7429900</v>
       </c>
       <c r="J94" s="3">
+        <v>-595000</v>
+      </c>
+      <c r="K94" s="3">
         <v>-8521800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>963400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1121600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>985900</v>
       </c>
     </row>
-    <row r="95" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3437,43 +3669,47 @@
       <c r="K95" s="3"/>
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
-    </row>
-    <row r="96" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N95" s="3"/>
+    </row>
+    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-1579900</v>
+        <v>-1855000</v>
       </c>
       <c r="E96" s="3">
-        <v>-1302200</v>
+        <v>-1599800</v>
       </c>
       <c r="F96" s="3">
-        <v>-1177800</v>
+        <v>-1318600</v>
       </c>
       <c r="G96" s="3">
-        <v>-1312100</v>
+        <v>-1192700</v>
       </c>
       <c r="H96" s="3">
-        <v>-1286400</v>
+        <v>-1328600</v>
       </c>
       <c r="I96" s="3">
-        <v>-578400</v>
+        <v>-1302600</v>
       </c>
       <c r="J96" s="3">
+        <v>-585700</v>
+      </c>
+      <c r="K96" s="3">
         <v>-416500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-1444400</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-1468900</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1477500</v>
       </c>
     </row>
-    <row r="97" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3507,8 +3743,11 @@
       <c r="M97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3542,8 +3781,11 @@
       <c r="M98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3577,109 +3819,121 @@
       <c r="M99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:13" x14ac:dyDescent="0.2">
+      <c r="N99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-3125500</v>
+        <v>4513500</v>
       </c>
       <c r="E100" s="3">
-        <v>6010800</v>
+        <v>-3164900</v>
       </c>
       <c r="F100" s="3">
-        <v>6413500</v>
+        <v>6086700</v>
       </c>
       <c r="G100" s="3">
-        <v>-7956500</v>
+        <v>6494400</v>
       </c>
       <c r="H100" s="3">
-        <v>-1209400</v>
+        <v>-8056900</v>
       </c>
       <c r="I100" s="3">
-        <v>-5154800</v>
+        <v>-1224700</v>
       </c>
       <c r="J100" s="3">
+        <v>-5219800</v>
+      </c>
+      <c r="K100" s="3">
         <v>368500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-643100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-3652800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>1833300</v>
       </c>
     </row>
-    <row r="101" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-475100</v>
+        <v>-629700</v>
       </c>
       <c r="E101" s="3">
-        <v>366500</v>
+        <v>-481100</v>
       </c>
       <c r="F101" s="3">
-        <v>3754500</v>
+        <v>371100</v>
       </c>
       <c r="G101" s="3">
-        <v>-3190000</v>
+        <v>3801900</v>
       </c>
       <c r="H101" s="3">
-        <v>2293800</v>
+        <v>-3230200</v>
       </c>
       <c r="I101" s="3">
-        <v>-2998500</v>
+        <v>2322700</v>
       </c>
       <c r="J101" s="3">
+        <v>-3036300</v>
+      </c>
+      <c r="K101" s="3">
         <v>-5536400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>4104400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>1847800</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>902800</v>
       </c>
     </row>
-    <row r="102" spans="3:13" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-26745100</v>
+        <v>-20292200</v>
       </c>
       <c r="E102" s="3">
-        <v>26759500</v>
+        <v>-27082400</v>
       </c>
       <c r="F102" s="3">
-        <v>51300</v>
+        <v>27097100</v>
       </c>
       <c r="G102" s="3">
-        <v>11050500</v>
+        <v>52000</v>
       </c>
       <c r="H102" s="3">
-        <v>17634400</v>
+        <v>11189800</v>
       </c>
       <c r="I102" s="3">
-        <v>10881300</v>
+        <v>17856800</v>
       </c>
       <c r="J102" s="3">
+        <v>11018600</v>
+      </c>
+      <c r="K102" s="3">
         <v>-23141900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>39852300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-8331100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>6128000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ANZGY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ANZGY_QTR_FIN.xlsx
@@ -719,25 +719,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>19863100</v>
+        <v>19982300</v>
       </c>
       <c r="E8" s="3">
-        <v>18038100</v>
+        <v>18146400</v>
       </c>
       <c r="F8" s="3">
-        <v>15213000</v>
+        <v>15304300</v>
       </c>
       <c r="G8" s="3">
-        <v>9262900</v>
+        <v>9318500</v>
       </c>
       <c r="H8" s="3">
-        <v>6467800</v>
+        <v>6506600</v>
       </c>
       <c r="I8" s="3">
-        <v>6429800</v>
+        <v>6468400</v>
       </c>
       <c r="J8" s="3">
-        <v>6582400</v>
+        <v>6621900</v>
       </c>
       <c r="K8" s="3">
         <v>6991900</v>
@@ -963,25 +963,25 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>-293800</v>
+        <v>-295600</v>
       </c>
       <c r="E15" s="3">
-        <v>-165200</v>
+        <v>-166200</v>
       </c>
       <c r="F15" s="3">
-        <v>-311200</v>
+        <v>-313000</v>
       </c>
       <c r="G15" s="3">
-        <v>-189900</v>
+        <v>-191000</v>
       </c>
       <c r="H15" s="3">
-        <v>-195200</v>
+        <v>-196400</v>
       </c>
       <c r="I15" s="3">
-        <v>-202600</v>
+        <v>-203800</v>
       </c>
       <c r="J15" s="3">
-        <v>-222500</v>
+        <v>-223900</v>
       </c>
       <c r="K15" s="3">
         <v>-340200</v>
@@ -1014,25 +1014,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>14646600</v>
+        <v>14734500</v>
       </c>
       <c r="E17" s="3">
-        <v>12730300</v>
+        <v>12806800</v>
       </c>
       <c r="F17" s="3">
-        <v>9638000</v>
+        <v>9695900</v>
       </c>
       <c r="G17" s="3">
-        <v>4117700</v>
+        <v>4142500</v>
       </c>
       <c r="H17" s="3">
-        <v>1547800</v>
+        <v>1557100</v>
       </c>
       <c r="I17" s="3">
-        <v>1598500</v>
+        <v>1608000</v>
       </c>
       <c r="J17" s="3">
-        <v>1600500</v>
+        <v>1610100</v>
       </c>
       <c r="K17" s="3">
         <v>3199900</v>
@@ -1052,25 +1052,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>5216500</v>
+        <v>5247800</v>
       </c>
       <c r="E18" s="3">
-        <v>5307700</v>
+        <v>5339600</v>
       </c>
       <c r="F18" s="3">
-        <v>5574900</v>
+        <v>5608400</v>
       </c>
       <c r="G18" s="3">
-        <v>5145200</v>
+        <v>5176100</v>
       </c>
       <c r="H18" s="3">
-        <v>4920000</v>
+        <v>4949500</v>
       </c>
       <c r="I18" s="3">
-        <v>4831300</v>
+        <v>4860300</v>
       </c>
       <c r="J18" s="3">
-        <v>4981900</v>
+        <v>5011800</v>
       </c>
       <c r="K18" s="3">
         <v>3792100</v>
@@ -1106,25 +1106,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-1978200</v>
+        <v>-1990100</v>
       </c>
       <c r="E20" s="3">
-        <v>-1932300</v>
+        <v>-1943900</v>
       </c>
       <c r="F20" s="3">
-        <v>-2229400</v>
+        <v>-2242800</v>
       </c>
       <c r="G20" s="3">
-        <v>-1784400</v>
+        <v>-1795100</v>
       </c>
       <c r="H20" s="3">
-        <v>-1565100</v>
+        <v>-1574500</v>
       </c>
       <c r="I20" s="3">
-        <v>-1793000</v>
+        <v>-1803800</v>
       </c>
       <c r="J20" s="3">
-        <v>-2066200</v>
+        <v>-2078600</v>
       </c>
       <c r="K20" s="3">
         <v>-1882500</v>
@@ -1144,25 +1144,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>3534700</v>
+        <v>3555900</v>
       </c>
       <c r="E21" s="3">
-        <v>3676600</v>
+        <v>3698700</v>
       </c>
       <c r="F21" s="3">
-        <v>3659300</v>
+        <v>3681300</v>
       </c>
       <c r="G21" s="3">
-        <v>3693300</v>
+        <v>3715500</v>
       </c>
       <c r="H21" s="3">
-        <v>3694000</v>
+        <v>3716100</v>
       </c>
       <c r="I21" s="3">
-        <v>3387500</v>
+        <v>3407800</v>
       </c>
       <c r="J21" s="3">
-        <v>3290900</v>
+        <v>3310600</v>
       </c>
       <c r="K21" s="3">
         <v>2421400</v>
@@ -1220,25 +1220,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>3238200</v>
+        <v>3257700</v>
       </c>
       <c r="E23" s="3">
-        <v>3375500</v>
+        <v>3395700</v>
       </c>
       <c r="F23" s="3">
-        <v>3345500</v>
+        <v>3365600</v>
       </c>
       <c r="G23" s="3">
-        <v>3360800</v>
+        <v>3381000</v>
       </c>
       <c r="H23" s="3">
-        <v>3354800</v>
+        <v>3375000</v>
       </c>
       <c r="I23" s="3">
-        <v>3038300</v>
+        <v>3056600</v>
       </c>
       <c r="J23" s="3">
-        <v>2915700</v>
+        <v>2933200</v>
       </c>
       <c r="K23" s="3">
         <v>1909500</v>
@@ -1258,25 +1258,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>958800</v>
+        <v>964600</v>
       </c>
       <c r="E24" s="3">
-        <v>1000100</v>
+        <v>1006100</v>
       </c>
       <c r="F24" s="3">
-        <v>967500</v>
+        <v>973300</v>
       </c>
       <c r="G24" s="3">
-        <v>959500</v>
+        <v>965200</v>
       </c>
       <c r="H24" s="3">
-        <v>999500</v>
+        <v>1005500</v>
       </c>
       <c r="I24" s="3">
-        <v>886800</v>
+        <v>892200</v>
       </c>
       <c r="J24" s="3">
-        <v>949500</v>
+        <v>955200</v>
       </c>
       <c r="K24" s="3">
         <v>567200</v>
@@ -1334,25 +1334,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>2279400</v>
+        <v>2293100</v>
       </c>
       <c r="E26" s="3">
-        <v>2375400</v>
+        <v>2389600</v>
       </c>
       <c r="F26" s="3">
-        <v>2378000</v>
+        <v>2392300</v>
       </c>
       <c r="G26" s="3">
-        <v>2401300</v>
+        <v>2415800</v>
       </c>
       <c r="H26" s="3">
-        <v>2355400</v>
+        <v>2369500</v>
       </c>
       <c r="I26" s="3">
-        <v>2151500</v>
+        <v>2164400</v>
       </c>
       <c r="J26" s="3">
-        <v>1966300</v>
+        <v>1978100</v>
       </c>
       <c r="K26" s="3">
         <v>1342300</v>
@@ -1372,25 +1372,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>2270100</v>
+        <v>2283700</v>
       </c>
       <c r="E27" s="3">
-        <v>2366000</v>
+        <v>2380200</v>
       </c>
       <c r="F27" s="3">
-        <v>2368700</v>
+        <v>2382900</v>
       </c>
       <c r="G27" s="3">
-        <v>2400700</v>
+        <v>2415100</v>
       </c>
       <c r="H27" s="3">
-        <v>2355400</v>
+        <v>2369500</v>
       </c>
       <c r="I27" s="3">
-        <v>2150800</v>
+        <v>2163700</v>
       </c>
       <c r="J27" s="3">
-        <v>1966300</v>
+        <v>1978100</v>
       </c>
       <c r="K27" s="3">
         <v>1342300</v>
@@ -1457,16 +1457,16 @@
         <v>0</v>
       </c>
       <c r="G29" s="3">
-        <v>-9300</v>
+        <v>-9400</v>
       </c>
       <c r="H29" s="3">
-        <v>-3300</v>
+        <v>-3400</v>
       </c>
       <c r="I29" s="3">
         <v>-6000</v>
       </c>
       <c r="J29" s="3">
-        <v>-5300</v>
+        <v>-5400</v>
       </c>
       <c r="K29" s="3">
         <v>-5300</v>
@@ -1562,25 +1562,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>1978200</v>
+        <v>1990100</v>
       </c>
       <c r="E32" s="3">
-        <v>1932300</v>
+        <v>1943900</v>
       </c>
       <c r="F32" s="3">
-        <v>2229400</v>
+        <v>2242800</v>
       </c>
       <c r="G32" s="3">
-        <v>1784400</v>
+        <v>1795100</v>
       </c>
       <c r="H32" s="3">
-        <v>1565100</v>
+        <v>1574500</v>
       </c>
       <c r="I32" s="3">
-        <v>1793000</v>
+        <v>1803800</v>
       </c>
       <c r="J32" s="3">
-        <v>2066200</v>
+        <v>2078600</v>
       </c>
       <c r="K32" s="3">
         <v>1882500</v>
@@ -1600,25 +1600,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>2270100</v>
+        <v>2283700</v>
       </c>
       <c r="E33" s="3">
-        <v>2366000</v>
+        <v>2380200</v>
       </c>
       <c r="F33" s="3">
-        <v>2368700</v>
+        <v>2382900</v>
       </c>
       <c r="G33" s="3">
-        <v>2391400</v>
+        <v>2405700</v>
       </c>
       <c r="H33" s="3">
-        <v>2352000</v>
+        <v>2366200</v>
       </c>
       <c r="I33" s="3">
-        <v>2144800</v>
+        <v>2157700</v>
       </c>
       <c r="J33" s="3">
-        <v>1960900</v>
+        <v>1972700</v>
       </c>
       <c r="K33" s="3">
         <v>1337100</v>
@@ -1676,25 +1676,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>2270100</v>
+        <v>2283700</v>
       </c>
       <c r="E35" s="3">
-        <v>2366000</v>
+        <v>2380200</v>
       </c>
       <c r="F35" s="3">
-        <v>2368700</v>
+        <v>2382900</v>
       </c>
       <c r="G35" s="3">
-        <v>2391400</v>
+        <v>2405700</v>
       </c>
       <c r="H35" s="3">
-        <v>2352000</v>
+        <v>2366200</v>
       </c>
       <c r="I35" s="3">
-        <v>2144800</v>
+        <v>2157700</v>
       </c>
       <c r="J35" s="3">
-        <v>1960900</v>
+        <v>1972700</v>
       </c>
       <c r="K35" s="3">
         <v>1337100</v>
@@ -1789,25 +1789,25 @@
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>98355900</v>
+        <v>98946300</v>
       </c>
       <c r="E41" s="3">
-        <v>122400000</v>
+        <v>123134800</v>
       </c>
       <c r="F41" s="3">
-        <v>147750000</v>
+        <v>148637000</v>
       </c>
       <c r="G41" s="3">
-        <v>119129100</v>
+        <v>119844300</v>
       </c>
       <c r="H41" s="3">
-        <v>120493000</v>
+        <v>121216400</v>
       </c>
       <c r="I41" s="3">
-        <v>109820200</v>
+        <v>110479500</v>
       </c>
       <c r="J41" s="3">
-        <v>93469900</v>
+        <v>94031000</v>
       </c>
       <c r="K41" s="3">
         <v>79933200</v>
@@ -1827,25 +1827,25 @@
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>65406700</v>
+        <v>65799300</v>
       </c>
       <c r="E42" s="3">
-        <v>70606500</v>
+        <v>71030400</v>
       </c>
       <c r="F42" s="3">
-        <v>62945400</v>
+        <v>63323200</v>
       </c>
       <c r="G42" s="3">
-        <v>92023400</v>
+        <v>92575800</v>
       </c>
       <c r="H42" s="3">
-        <v>63588300</v>
+        <v>63970100</v>
       </c>
       <c r="I42" s="3">
-        <v>61692700</v>
+        <v>62063100</v>
       </c>
       <c r="J42" s="3">
-        <v>108644200</v>
+        <v>109296400</v>
       </c>
       <c r="K42" s="3">
         <v>131963200</v>
@@ -2017,25 +2017,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>945500</v>
+        <v>951200</v>
       </c>
       <c r="E47" s="3">
-        <v>1565100</v>
+        <v>1574500</v>
       </c>
       <c r="F47" s="3">
-        <v>1501200</v>
+        <v>1510200</v>
       </c>
       <c r="G47" s="3">
-        <v>1453200</v>
+        <v>1461900</v>
       </c>
       <c r="H47" s="3">
-        <v>1344600</v>
+        <v>1352700</v>
       </c>
       <c r="I47" s="3">
-        <v>1313900</v>
+        <v>1321800</v>
       </c>
       <c r="J47" s="3">
-        <v>1235300</v>
+        <v>1242700</v>
       </c>
       <c r="K47" s="3">
         <v>1423900</v>
@@ -2055,25 +2055,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1335900</v>
+        <v>1344000</v>
       </c>
       <c r="E48" s="3">
-        <v>1367900</v>
+        <v>1376100</v>
       </c>
       <c r="F48" s="3">
-        <v>1525200</v>
+        <v>1534300</v>
       </c>
       <c r="G48" s="3">
-        <v>1619800</v>
+        <v>1629500</v>
       </c>
       <c r="H48" s="3">
-        <v>1800300</v>
+        <v>1811200</v>
       </c>
       <c r="I48" s="3">
-        <v>1821700</v>
+        <v>1832600</v>
       </c>
       <c r="J48" s="3">
-        <v>1860300</v>
+        <v>1871500</v>
       </c>
       <c r="K48" s="3">
         <v>1982600</v>
@@ -2093,25 +2093,25 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2663900</v>
+        <v>2679900</v>
       </c>
       <c r="E49" s="3">
-        <v>2703800</v>
+        <v>2720100</v>
       </c>
       <c r="F49" s="3">
-        <v>2689900</v>
+        <v>2706000</v>
       </c>
       <c r="G49" s="3">
-        <v>2583200</v>
+        <v>2598800</v>
       </c>
       <c r="H49" s="3">
-        <v>2710500</v>
+        <v>2726800</v>
       </c>
       <c r="I49" s="3">
-        <v>2747800</v>
+        <v>2764300</v>
       </c>
       <c r="J49" s="3">
-        <v>2681200</v>
+        <v>2697300</v>
       </c>
       <c r="K49" s="3">
         <v>2881400</v>
@@ -2207,25 +2207,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2098200</v>
+        <v>2110800</v>
       </c>
       <c r="E52" s="3">
-        <v>2230800</v>
+        <v>2244200</v>
       </c>
       <c r="F52" s="3">
-        <v>1981600</v>
+        <v>1993500</v>
       </c>
       <c r="G52" s="3">
-        <v>2254800</v>
+        <v>2268300</v>
       </c>
       <c r="H52" s="3">
-        <v>1934300</v>
+        <v>1945900</v>
       </c>
       <c r="I52" s="3">
-        <v>1558500</v>
+        <v>1567800</v>
       </c>
       <c r="J52" s="3">
-        <v>1402600</v>
+        <v>1411000</v>
       </c>
       <c r="K52" s="3">
         <v>1397600</v>
@@ -2283,25 +2283,25 @@
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>726066400</v>
+        <v>730425200</v>
       </c>
       <c r="E54" s="3">
-        <v>736689900</v>
+        <v>741112500</v>
       </c>
       <c r="F54" s="3">
-        <v>740417200</v>
+        <v>744862200</v>
       </c>
       <c r="G54" s="3">
-        <v>723421200</v>
+        <v>727764100</v>
       </c>
       <c r="H54" s="3">
-        <v>677867600</v>
+        <v>681937100</v>
       </c>
       <c r="I54" s="3">
-        <v>652212400</v>
+        <v>656127800</v>
       </c>
       <c r="J54" s="3">
-        <v>678519300</v>
+        <v>682592600</v>
       </c>
       <c r="K54" s="3">
         <v>685824200</v>
@@ -2353,25 +2353,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>11389700</v>
+        <v>11458100</v>
       </c>
       <c r="E57" s="3">
-        <v>10059100</v>
+        <v>10119500</v>
       </c>
       <c r="F57" s="3">
-        <v>8699900</v>
+        <v>8752100</v>
       </c>
       <c r="G57" s="3">
-        <v>6553100</v>
+        <v>6592400</v>
       </c>
       <c r="H57" s="3">
-        <v>7048800</v>
+        <v>7091100</v>
       </c>
       <c r="I57" s="3">
-        <v>5761500</v>
+        <v>5796100</v>
       </c>
       <c r="J57" s="3">
-        <v>5702200</v>
+        <v>5736400</v>
       </c>
       <c r="K57" s="3">
         <v>6006200</v>
@@ -2429,25 +2429,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>133900</v>
+        <v>134700</v>
       </c>
       <c r="E59" s="3">
-        <v>203200</v>
+        <v>204400</v>
       </c>
       <c r="F59" s="3">
-        <v>231200</v>
+        <v>232600</v>
       </c>
       <c r="G59" s="3">
-        <v>552400</v>
+        <v>555700</v>
       </c>
       <c r="H59" s="3">
-        <v>213200</v>
+        <v>214500</v>
       </c>
       <c r="I59" s="3">
-        <v>279200</v>
+        <v>280900</v>
       </c>
       <c r="J59" s="3">
-        <v>135300</v>
+        <v>136100</v>
       </c>
       <c r="K59" s="3">
         <v>229600</v>
@@ -2505,25 +2505,25 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>84692700</v>
+        <v>85201200</v>
       </c>
       <c r="E61" s="3">
-        <v>77300100</v>
+        <v>77764200</v>
       </c>
       <c r="F61" s="3">
-        <v>70732400</v>
+        <v>71157000</v>
       </c>
       <c r="G61" s="3">
-        <v>62455000</v>
+        <v>62829900</v>
       </c>
       <c r="H61" s="3">
-        <v>58118700</v>
+        <v>58467600</v>
       </c>
       <c r="I61" s="3">
-        <v>67332300</v>
+        <v>67736500</v>
       </c>
       <c r="J61" s="3">
-        <v>71709200</v>
+        <v>72139700</v>
       </c>
       <c r="K61" s="3">
         <v>78741500</v>
@@ -2543,25 +2543,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1546500</v>
+        <v>1555800</v>
       </c>
       <c r="E62" s="3">
-        <v>1577800</v>
+        <v>1587300</v>
       </c>
       <c r="F62" s="3">
-        <v>1576500</v>
+        <v>1585900</v>
       </c>
       <c r="G62" s="3">
-        <v>1668400</v>
+        <v>1678400</v>
       </c>
       <c r="H62" s="3">
-        <v>1951600</v>
+        <v>1963300</v>
       </c>
       <c r="I62" s="3">
-        <v>1922900</v>
+        <v>1934500</v>
       </c>
       <c r="J62" s="3">
-        <v>2058900</v>
+        <v>2071200</v>
       </c>
       <c r="K62" s="3">
         <v>2141800</v>
@@ -2695,25 +2695,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>679221600</v>
+        <v>683299100</v>
       </c>
       <c r="E66" s="3">
-        <v>690385400</v>
+        <v>694530000</v>
       </c>
       <c r="F66" s="3">
-        <v>694405900</v>
+        <v>698574600</v>
       </c>
       <c r="G66" s="3">
-        <v>679507400</v>
+        <v>683586700</v>
       </c>
       <c r="H66" s="3">
-        <v>636725600</v>
+        <v>640548100</v>
       </c>
       <c r="I66" s="3">
-        <v>609792400</v>
+        <v>613453200</v>
       </c>
       <c r="J66" s="3">
-        <v>636831500</v>
+        <v>640654600</v>
       </c>
       <c r="K66" s="3">
         <v>645497300</v>
@@ -2901,25 +2901,25 @@
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>28511600</v>
+        <v>28682800</v>
       </c>
       <c r="E72" s="3">
-        <v>28123900</v>
+        <v>28292700</v>
       </c>
       <c r="F72" s="3">
-        <v>27355600</v>
+        <v>27519800</v>
       </c>
       <c r="G72" s="3">
-        <v>26500100</v>
+        <v>26659200</v>
       </c>
       <c r="H72" s="3">
-        <v>25392700</v>
+        <v>25545100</v>
       </c>
       <c r="I72" s="3">
-        <v>24324600</v>
+        <v>24470600</v>
       </c>
       <c r="J72" s="3">
-        <v>23483100</v>
+        <v>23624100</v>
       </c>
       <c r="K72" s="3">
         <v>21923200</v>
@@ -3053,25 +3053,25 @@
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>46844900</v>
+        <v>47126100</v>
       </c>
       <c r="E76" s="3">
-        <v>46304500</v>
+        <v>46582500</v>
       </c>
       <c r="F76" s="3">
-        <v>46011300</v>
+        <v>46287600</v>
       </c>
       <c r="G76" s="3">
-        <v>43913800</v>
+        <v>44177500</v>
       </c>
       <c r="H76" s="3">
-        <v>41142000</v>
+        <v>41389000</v>
       </c>
       <c r="I76" s="3">
-        <v>42420000</v>
+        <v>42674600</v>
       </c>
       <c r="J76" s="3">
-        <v>41687700</v>
+        <v>41938000</v>
       </c>
       <c r="K76" s="3">
         <v>40326800</v>
@@ -3172,25 +3172,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>2270100</v>
+        <v>2283700</v>
       </c>
       <c r="E81" s="3">
-        <v>2366000</v>
+        <v>2380200</v>
       </c>
       <c r="F81" s="3">
-        <v>2368700</v>
+        <v>2382900</v>
       </c>
       <c r="G81" s="3">
-        <v>2391400</v>
+        <v>2405700</v>
       </c>
       <c r="H81" s="3">
-        <v>2352000</v>
+        <v>2366200</v>
       </c>
       <c r="I81" s="3">
-        <v>2144800</v>
+        <v>2157700</v>
       </c>
       <c r="J81" s="3">
-        <v>1960900</v>
+        <v>1972700</v>
       </c>
       <c r="K81" s="3">
         <v>1337100</v>
@@ -3226,25 +3226,25 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>296500</v>
+        <v>298300</v>
       </c>
       <c r="E83" s="3">
-        <v>301200</v>
+        <v>303000</v>
       </c>
       <c r="F83" s="3">
-        <v>313800</v>
+        <v>315700</v>
       </c>
       <c r="G83" s="3">
-        <v>332500</v>
+        <v>334500</v>
       </c>
       <c r="H83" s="3">
-        <v>339100</v>
+        <v>341200</v>
       </c>
       <c r="I83" s="3">
-        <v>349100</v>
+        <v>351200</v>
       </c>
       <c r="J83" s="3">
-        <v>375100</v>
+        <v>377400</v>
       </c>
       <c r="K83" s="3">
         <v>511900</v>
@@ -3454,25 +3454,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-10392300</v>
+        <v>-10454700</v>
       </c>
       <c r="E89" s="3">
-        <v>-21967200</v>
+        <v>-22099100</v>
       </c>
       <c r="F89" s="3">
-        <v>26290200</v>
+        <v>26448000</v>
       </c>
       <c r="G89" s="3">
-        <v>-8305400</v>
+        <v>-8355300</v>
       </c>
       <c r="H89" s="3">
-        <v>21748700</v>
+        <v>21879300</v>
       </c>
       <c r="I89" s="3">
-        <v>9328900</v>
+        <v>9384900</v>
       </c>
       <c r="J89" s="3">
-        <v>19869700</v>
+        <v>19989000</v>
       </c>
       <c r="K89" s="3">
         <v>-1554900</v>
@@ -3622,25 +3622,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-13783700</v>
+        <v>-13866500</v>
       </c>
       <c r="E94" s="3">
-        <v>-1469200</v>
+        <v>-1478000</v>
       </c>
       <c r="F94" s="3">
-        <v>-5650900</v>
+        <v>-5684800</v>
       </c>
       <c r="G94" s="3">
-        <v>-1938900</v>
+        <v>-1950600</v>
       </c>
       <c r="H94" s="3">
-        <v>728300</v>
+        <v>732600</v>
       </c>
       <c r="I94" s="3">
-        <v>7429900</v>
+        <v>7474500</v>
       </c>
       <c r="J94" s="3">
-        <v>-595000</v>
+        <v>-598600</v>
       </c>
       <c r="K94" s="3">
         <v>-8521800</v>
@@ -3676,25 +3676,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-1855000</v>
+        <v>-1866100</v>
       </c>
       <c r="E96" s="3">
-        <v>-1599800</v>
+        <v>-1609400</v>
       </c>
       <c r="F96" s="3">
-        <v>-1318600</v>
+        <v>-1326500</v>
       </c>
       <c r="G96" s="3">
-        <v>-1192700</v>
+        <v>-1199800</v>
       </c>
       <c r="H96" s="3">
-        <v>-1328600</v>
+        <v>-1336600</v>
       </c>
       <c r="I96" s="3">
-        <v>-1302600</v>
+        <v>-1310400</v>
       </c>
       <c r="J96" s="3">
-        <v>-585700</v>
+        <v>-589200</v>
       </c>
       <c r="K96" s="3">
         <v>-416500</v>
@@ -3828,25 +3828,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>4513500</v>
+        <v>4540600</v>
       </c>
       <c r="E100" s="3">
-        <v>-3164900</v>
+        <v>-3183900</v>
       </c>
       <c r="F100" s="3">
-        <v>6086700</v>
+        <v>6123200</v>
       </c>
       <c r="G100" s="3">
-        <v>6494400</v>
+        <v>6533400</v>
       </c>
       <c r="H100" s="3">
-        <v>-8056900</v>
+        <v>-8105300</v>
       </c>
       <c r="I100" s="3">
-        <v>-1224700</v>
+        <v>-1232000</v>
       </c>
       <c r="J100" s="3">
-        <v>-5219800</v>
+        <v>-5251100</v>
       </c>
       <c r="K100" s="3">
         <v>368500</v>
@@ -3866,25 +3866,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-629700</v>
+        <v>-633400</v>
       </c>
       <c r="E101" s="3">
-        <v>-481100</v>
+        <v>-484000</v>
       </c>
       <c r="F101" s="3">
-        <v>371100</v>
+        <v>373400</v>
       </c>
       <c r="G101" s="3">
-        <v>3801900</v>
+        <v>3824700</v>
       </c>
       <c r="H101" s="3">
-        <v>-3230200</v>
+        <v>-3249600</v>
       </c>
       <c r="I101" s="3">
-        <v>2322700</v>
+        <v>2336700</v>
       </c>
       <c r="J101" s="3">
-        <v>-3036300</v>
+        <v>-3054600</v>
       </c>
       <c r="K101" s="3">
         <v>-5536400</v>
@@ -3904,25 +3904,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-20292200</v>
+        <v>-20414000</v>
       </c>
       <c r="E102" s="3">
-        <v>-27082400</v>
+        <v>-27245000</v>
       </c>
       <c r="F102" s="3">
-        <v>27097100</v>
+        <v>27259800</v>
       </c>
       <c r="G102" s="3">
-        <v>52000</v>
+        <v>52300</v>
       </c>
       <c r="H102" s="3">
-        <v>11189800</v>
+        <v>11257000</v>
       </c>
       <c r="I102" s="3">
-        <v>17856800</v>
+        <v>17964000</v>
       </c>
       <c r="J102" s="3">
-        <v>11018600</v>
+        <v>11084800</v>
       </c>
       <c r="K102" s="3">
         <v>-23141900</v>

--- a/AAII_Financials/Quarterly/ANZGY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ANZGY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="92">
   <si>
     <t>ANZGY</t>
   </si>
@@ -656,103 +656,115 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:N102"/>
+  <dimension ref="A5:P102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="I7" s="2">
+        <v>45107</v>
+      </c>
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
-        <v>44834</v>
-      </c>
-      <c r="H7" s="2">
-        <v>44651</v>
-      </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>44469</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44286</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44104</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>43921</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>43738</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="3">
-        <v>19982300</v>
-      </c>
-      <c r="E8" s="3">
-        <v>18146400</v>
-      </c>
-      <c r="F8" s="3">
-        <v>15304300</v>
-      </c>
-      <c r="G8" s="3">
-        <v>9318500</v>
-      </c>
-      <c r="H8" s="3">
-        <v>6506600</v>
-      </c>
-      <c r="I8" s="3">
+      <c r="D8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K8" s="3">
         <v>6468400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>6621900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>6991900</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>8946500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>9955500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>10524200</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -789,8 +801,14 @@
       <c r="N9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -827,8 +845,14 @@
       <c r="N10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -843,8 +867,10 @@
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O11" s="3"/>
+      <c r="P11" s="3"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -881,8 +907,14 @@
       <c r="N12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -919,31 +951,37 @@
       <c r="N13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O13" s="3">
+        <v>0</v>
+      </c>
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -957,46 +995,58 @@
       <c r="N14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3">
-        <v>-295600</v>
-      </c>
-      <c r="E15" s="3">
-        <v>-166200</v>
-      </c>
-      <c r="F15" s="3">
-        <v>-313000</v>
-      </c>
-      <c r="G15" s="3">
-        <v>-191000</v>
-      </c>
-      <c r="H15" s="3">
-        <v>-196400</v>
-      </c>
-      <c r="I15" s="3">
+      <c r="D15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K15" s="3">
         <v>-203800</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>-223900</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>-340200</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>-221100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>-235300</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>-222100</v>
       </c>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1008,84 +1058,98 @@
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
-    </row>
-    <row r="17" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O16" s="3"/>
+      <c r="P16" s="3"/>
+    </row>
+    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3">
-        <v>14734500</v>
-      </c>
-      <c r="E17" s="3">
-        <v>12806800</v>
-      </c>
-      <c r="F17" s="3">
-        <v>9695900</v>
-      </c>
-      <c r="G17" s="3">
-        <v>4142500</v>
-      </c>
-      <c r="H17" s="3">
-        <v>1557100</v>
-      </c>
-      <c r="I17" s="3">
+      <c r="D17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K17" s="3">
         <v>1608000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1610100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>3199900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>5349800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>5581100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>5972500</v>
       </c>
     </row>
-    <row r="18" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3">
-        <v>5247800</v>
-      </c>
-      <c r="E18" s="3">
-        <v>5339600</v>
-      </c>
-      <c r="F18" s="3">
-        <v>5608400</v>
-      </c>
-      <c r="G18" s="3">
-        <v>5176100</v>
-      </c>
-      <c r="H18" s="3">
-        <v>4949500</v>
-      </c>
-      <c r="I18" s="3">
+      <c r="D18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K18" s="3">
         <v>4860300</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>5011800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>3792100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>3596800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>4374400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>4551700</v>
       </c>
     </row>
-    <row r="19" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1100,107 +1164,121 @@
       <c r="L19" s="3"/>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
-    </row>
-    <row r="20" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O19" s="3"/>
+      <c r="P19" s="3"/>
+    </row>
+    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3">
-        <v>-1990100</v>
-      </c>
-      <c r="E20" s="3">
-        <v>-1943900</v>
-      </c>
-      <c r="F20" s="3">
-        <v>-2242800</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-1795100</v>
-      </c>
-      <c r="H20" s="3">
-        <v>-1574500</v>
-      </c>
-      <c r="I20" s="3">
+      <c r="D20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K20" s="3">
         <v>-1803800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>-2078600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>-1882500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-1902100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-1485400</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-1562500</v>
       </c>
     </row>
-    <row r="21" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3">
-        <v>3555900</v>
-      </c>
-      <c r="E21" s="3">
-        <v>3698700</v>
-      </c>
-      <c r="F21" s="3">
-        <v>3681300</v>
-      </c>
-      <c r="G21" s="3">
-        <v>3715500</v>
-      </c>
-      <c r="H21" s="3">
-        <v>3716100</v>
-      </c>
-      <c r="I21" s="3">
+      <c r="D21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K21" s="3">
         <v>3407800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>3310600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>2421400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>2092100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>3181000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>3271300</v>
       </c>
     </row>
-    <row r="22" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3">
-        <v>0</v>
-      </c>
-      <c r="E22" s="3">
-        <v>0</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
-      </c>
-      <c r="G22" s="3">
-        <v>0</v>
-      </c>
-      <c r="H22" s="3">
-        <v>0</v>
-      </c>
-      <c r="I22" s="3">
-        <v>0</v>
-      </c>
-      <c r="J22" s="3">
-        <v>0</v>
+      <c r="D22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K22" s="3">
         <v>0</v>
@@ -1214,84 +1292,102 @@
       <c r="N22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O22" s="3">
+        <v>0</v>
+      </c>
+      <c r="P22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="D23" s="3">
-        <v>3257700</v>
-      </c>
-      <c r="E23" s="3">
-        <v>3395700</v>
-      </c>
-      <c r="F23" s="3">
-        <v>3365600</v>
-      </c>
-      <c r="G23" s="3">
-        <v>3381000</v>
-      </c>
-      <c r="H23" s="3">
-        <v>3375000</v>
-      </c>
-      <c r="I23" s="3">
+      <c r="D23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K23" s="3">
         <v>3056600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>2933200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>1909500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>1694700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>2889100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>2989200</v>
       </c>
     </row>
-    <row r="24" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="D24" s="3">
-        <v>964600</v>
-      </c>
-      <c r="E24" s="3">
-        <v>1006100</v>
-      </c>
-      <c r="F24" s="3">
-        <v>973300</v>
-      </c>
-      <c r="G24" s="3">
-        <v>965200</v>
-      </c>
-      <c r="H24" s="3">
-        <v>1005500</v>
-      </c>
-      <c r="I24" s="3">
+      <c r="D24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K24" s="3">
         <v>892200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>955200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>567200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>634000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>873200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>846200</v>
       </c>
     </row>
-    <row r="25" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1328,84 +1424,102 @@
       <c r="N25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O25" s="3">
+        <v>0</v>
+      </c>
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3">
-        <v>2293100</v>
-      </c>
-      <c r="E26" s="3">
-        <v>2389600</v>
-      </c>
-      <c r="F26" s="3">
-        <v>2392300</v>
-      </c>
-      <c r="G26" s="3">
-        <v>2415800</v>
-      </c>
-      <c r="H26" s="3">
-        <v>2369500</v>
-      </c>
-      <c r="I26" s="3">
+      <c r="D26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K26" s="3">
         <v>2164400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>1978100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>1342300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>1060600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>2015900</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>2143100</v>
       </c>
     </row>
-    <row r="27" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3">
-        <v>2283700</v>
-      </c>
-      <c r="E27" s="3">
-        <v>2380200</v>
-      </c>
-      <c r="F27" s="3">
-        <v>2382900</v>
-      </c>
-      <c r="G27" s="3">
-        <v>2415100</v>
-      </c>
-      <c r="H27" s="3">
-        <v>2369500</v>
-      </c>
-      <c r="I27" s="3">
+      <c r="D27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K27" s="3">
         <v>2163700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>1978100</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>1342300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>1060000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>2011900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>2137100</v>
       </c>
     </row>
-    <row r="28" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1442,46 +1556,58 @@
       <c r="N28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O28" s="3">
+        <v>0</v>
+      </c>
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3">
-        <v>-9400</v>
-      </c>
-      <c r="H29" s="3">
-        <v>-3400</v>
-      </c>
-      <c r="I29" s="3">
+      <c r="E29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K29" s="3">
         <v>-6000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="L29" s="3">
         <v>-5400</v>
       </c>
-      <c r="K29" s="3">
+      <c r="M29" s="3">
         <v>-5300</v>
       </c>
-      <c r="L29" s="3">
+      <c r="N29" s="3">
         <v>-58300</v>
       </c>
-      <c r="M29" s="3">
+      <c r="O29" s="3">
         <v>-179900</v>
       </c>
-      <c r="N29" s="3">
+      <c r="P29" s="3">
         <v>-46100</v>
       </c>
     </row>
-    <row r="30" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1518,8 +1644,14 @@
       <c r="N30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1556,84 +1688,102 @@
       <c r="N31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O31" s="3">
+        <v>0</v>
+      </c>
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3">
-        <v>1990100</v>
-      </c>
-      <c r="E32" s="3">
-        <v>1943900</v>
-      </c>
-      <c r="F32" s="3">
-        <v>2242800</v>
-      </c>
-      <c r="G32" s="3">
-        <v>1795100</v>
-      </c>
-      <c r="H32" s="3">
-        <v>1574500</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="D32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K32" s="3">
         <v>1803800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>2078600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>1882500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>1902100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>1485400</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>1562500</v>
       </c>
     </row>
-    <row r="33" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3">
-        <v>2283700</v>
-      </c>
-      <c r="E33" s="3">
-        <v>2380200</v>
-      </c>
-      <c r="F33" s="3">
-        <v>2382900</v>
-      </c>
-      <c r="G33" s="3">
-        <v>2405700</v>
-      </c>
-      <c r="H33" s="3">
-        <v>2366200</v>
-      </c>
-      <c r="I33" s="3">
+      <c r="D33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K33" s="3">
         <v>2157700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>1972700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>1337100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>1001600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>1832000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>2091000</v>
       </c>
     </row>
-    <row r="34" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1670,89 +1820,107 @@
       <c r="N34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O34" s="3">
+        <v>0</v>
+      </c>
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3">
-        <v>2283700</v>
-      </c>
-      <c r="E35" s="3">
-        <v>2380200</v>
-      </c>
-      <c r="F35" s="3">
-        <v>2382900</v>
-      </c>
-      <c r="G35" s="3">
-        <v>2405700</v>
-      </c>
-      <c r="H35" s="3">
-        <v>2366200</v>
-      </c>
-      <c r="I35" s="3">
+      <c r="D35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K35" s="3">
         <v>2157700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>1972700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>1337100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>1001600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>1832000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>2091000</v>
       </c>
     </row>
-    <row r="37" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="I38" s="2">
+        <v>45107</v>
+      </c>
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
-        <v>44834</v>
-      </c>
-      <c r="H38" s="2">
-        <v>44651</v>
-      </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>44469</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44286</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44104</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>43921</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>43738</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="39" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1767,8 +1935,10 @@
       <c r="L39" s="3"/>
       <c r="M39" s="3"/>
       <c r="N39" s="3"/>
-    </row>
-    <row r="40" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O39" s="3"/>
+      <c r="P39" s="3"/>
+    </row>
+    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1783,107 +1953,121 @@
       <c r="L40" s="3"/>
       <c r="M40" s="3"/>
       <c r="N40" s="3"/>
-    </row>
-    <row r="41" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O40" s="3"/>
+      <c r="P40" s="3"/>
+    </row>
+    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
-        <v>98946300</v>
+        <v>74077500</v>
       </c>
       <c r="E41" s="3">
-        <v>123134800</v>
+        <v>71285000</v>
       </c>
       <c r="F41" s="3">
-        <v>148637000</v>
+        <v>89792000</v>
       </c>
       <c r="G41" s="3">
-        <v>119844300</v>
+        <v>93862300</v>
       </c>
       <c r="H41" s="3">
-        <v>121216400</v>
+        <v>88044800</v>
       </c>
       <c r="I41" s="3">
+        <v>90810600</v>
+      </c>
+      <c r="J41" s="3">
+        <v>140012100</v>
+      </c>
+      <c r="K41" s="3">
         <v>110479500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>94031000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>79933200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>101864800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>61620500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>70159800</v>
       </c>
     </row>
-    <row r="42" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
-        <v>65799300</v>
+        <v>100013900</v>
       </c>
       <c r="E42" s="3">
-        <v>71030400</v>
+        <v>96243700</v>
       </c>
       <c r="F42" s="3">
-        <v>63323200</v>
+        <v>58639100</v>
       </c>
       <c r="G42" s="3">
-        <v>92575800</v>
+        <v>61297200</v>
       </c>
       <c r="H42" s="3">
-        <v>63970100</v>
+        <v>83320000</v>
       </c>
       <c r="I42" s="3">
+        <v>85937400</v>
+      </c>
+      <c r="J42" s="3">
+        <v>57148100</v>
+      </c>
+      <c r="K42" s="3">
         <v>62063100</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>109296400</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>131963200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>155272400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>117856900</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>88366600</v>
       </c>
     </row>
-    <row r="43" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>0</v>
+        <v>31900</v>
       </c>
       <c r="E43" s="3">
-        <v>0</v>
+        <v>30700</v>
       </c>
       <c r="F43" s="3">
-        <v>0</v>
+        <v>29300</v>
       </c>
       <c r="G43" s="3">
-        <v>0</v>
+        <v>30700</v>
       </c>
       <c r="H43" s="3">
-        <v>0</v>
+        <v>73600</v>
       </c>
       <c r="I43" s="3">
-        <v>0</v>
+        <v>75900</v>
       </c>
       <c r="J43" s="3">
-        <v>0</v>
+        <v>32900</v>
       </c>
       <c r="K43" s="3">
         <v>0</v>
@@ -1897,31 +2081,37 @@
       <c r="N43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O43" s="3">
+        <v>0</v>
+      </c>
+      <c r="P43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -1935,31 +2125,37 @@
       <c r="N44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O44" s="3">
+        <v>0</v>
+      </c>
+      <c r="P44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>10798000</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>10391000</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>7857800</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>8214000</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>11555100</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>11918100</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>10906600</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -1973,31 +2169,37 @@
       <c r="N45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O45" s="3">
+        <v>0</v>
+      </c>
+      <c r="P45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>185382400</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>178394000</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>156772100</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>163878700</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>183410300</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>189172000</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>208532800</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -2011,122 +2213,146 @@
       <c r="N46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O46" s="3">
+        <v>0</v>
+      </c>
+      <c r="P46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>951200</v>
+        <v>98449000</v>
       </c>
       <c r="E47" s="3">
-        <v>1574500</v>
+        <v>94737800</v>
       </c>
       <c r="F47" s="3">
-        <v>1510200</v>
+        <v>77615300</v>
       </c>
       <c r="G47" s="3">
-        <v>1461900</v>
+        <v>81133600</v>
       </c>
       <c r="H47" s="3">
-        <v>1352700</v>
+        <v>64385400</v>
       </c>
       <c r="I47" s="3">
+        <v>66408000</v>
+      </c>
+      <c r="J47" s="3">
+        <v>64524200</v>
+      </c>
+      <c r="K47" s="3">
         <v>1321800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>1242700</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>1423900</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>1499500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>1948700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>1803700</v>
       </c>
     </row>
-    <row r="48" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>1344000</v>
+        <v>1540600</v>
       </c>
       <c r="E48" s="3">
-        <v>1376100</v>
+        <v>1482500</v>
       </c>
       <c r="F48" s="3">
-        <v>1534300</v>
+        <v>1495300</v>
       </c>
       <c r="G48" s="3">
-        <v>1629500</v>
+        <v>1563100</v>
       </c>
       <c r="H48" s="3">
-        <v>1811200</v>
+        <v>1324800</v>
       </c>
       <c r="I48" s="3">
+        <v>1366400</v>
+      </c>
+      <c r="J48" s="3">
+        <v>1534900</v>
+      </c>
+      <c r="K48" s="3">
         <v>1832600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>1871500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>1982600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>2081700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>1267900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>1227700</v>
       </c>
     </row>
-    <row r="49" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>2679900</v>
+        <v>3821000</v>
       </c>
       <c r="E49" s="3">
-        <v>2720100</v>
+        <v>3676900</v>
       </c>
       <c r="F49" s="3">
-        <v>2706000</v>
+        <v>2547800</v>
       </c>
       <c r="G49" s="3">
-        <v>2598800</v>
+        <v>2663300</v>
       </c>
       <c r="H49" s="3">
-        <v>2726800</v>
+        <v>2618600</v>
       </c>
       <c r="I49" s="3">
+        <v>2700800</v>
+      </c>
+      <c r="J49" s="3">
+        <v>2707000</v>
+      </c>
+      <c r="K49" s="3">
         <v>2764300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>2697300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>2881400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>3213600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>3203400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>3306200</v>
       </c>
     </row>
-    <row r="50" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2163,8 +2389,14 @@
       <c r="N50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O50" s="3">
+        <v>0</v>
+      </c>
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2201,46 +2433,58 @@
       <c r="N51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O51" s="3">
+        <v>0</v>
+      </c>
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>2110800</v>
+        <v>3727400</v>
       </c>
       <c r="E52" s="3">
-        <v>2244200</v>
+        <v>3586900</v>
       </c>
       <c r="F52" s="3">
-        <v>1993500</v>
+        <v>3576800</v>
       </c>
       <c r="G52" s="3">
-        <v>2268300</v>
+        <v>3738900</v>
       </c>
       <c r="H52" s="3">
-        <v>1945900</v>
+        <v>3311000</v>
       </c>
       <c r="I52" s="3">
+        <v>3415000</v>
+      </c>
+      <c r="J52" s="3">
+        <v>3094600</v>
+      </c>
+      <c r="K52" s="3">
         <v>1567800</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>1411000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>1397600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>1177300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>2100200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>29454000</v>
       </c>
     </row>
-    <row r="53" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2277,46 +2521,58 @@
       <c r="N53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O53" s="3">
+        <v>0</v>
+      </c>
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
-        <v>730425200</v>
+        <v>852190900</v>
       </c>
       <c r="E54" s="3">
-        <v>741112500</v>
+        <v>820066100</v>
       </c>
       <c r="F54" s="3">
-        <v>744862200</v>
+        <v>710882300</v>
       </c>
       <c r="G54" s="3">
-        <v>727764100</v>
+        <v>743107000</v>
       </c>
       <c r="H54" s="3">
-        <v>681937100</v>
+        <v>713456200</v>
       </c>
       <c r="I54" s="3">
+        <v>735868900</v>
+      </c>
+      <c r="J54" s="3">
+        <v>745121700</v>
+      </c>
+      <c r="K54" s="3">
         <v>656127800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>682592600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>685824200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>745515800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>646569300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>645997900</v>
       </c>
     </row>
-    <row r="55" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2331,8 +2587,10 @@
       <c r="L55" s="3"/>
       <c r="M55" s="3"/>
       <c r="N55" s="3"/>
-    </row>
-    <row r="56" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O55" s="3"/>
+      <c r="P55" s="3"/>
+    </row>
+    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2347,69 +2605,77 @@
       <c r="L56" s="3"/>
       <c r="M56" s="3"/>
       <c r="N56" s="3"/>
-    </row>
-    <row r="57" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O56" s="3"/>
+      <c r="P56" s="3"/>
+    </row>
+    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>11458100</v>
+        <v>593473600</v>
       </c>
       <c r="E57" s="3">
-        <v>10119500</v>
+        <v>571101500</v>
       </c>
       <c r="F57" s="3">
-        <v>8752100</v>
+        <v>496752500</v>
       </c>
       <c r="G57" s="3">
-        <v>6592400</v>
+        <v>519270600</v>
       </c>
       <c r="H57" s="3">
-        <v>7091100</v>
+        <v>504355700</v>
       </c>
       <c r="I57" s="3">
+        <v>520199700</v>
+      </c>
+      <c r="J57" s="3">
+        <v>538939200</v>
+      </c>
+      <c r="K57" s="3">
         <v>5796100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>5736400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>6006200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>6830500</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>5250900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>5035400</v>
       </c>
     </row>
-    <row r="58" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>0</v>
+        <v>95871900</v>
       </c>
       <c r="E58" s="3">
-        <v>0</v>
+        <v>92257800</v>
       </c>
       <c r="F58" s="3">
-        <v>0</v>
+        <v>57480900</v>
       </c>
       <c r="G58" s="3">
-        <v>0</v>
+        <v>60086600</v>
       </c>
       <c r="H58" s="3">
-        <v>0</v>
+        <v>72685700</v>
       </c>
       <c r="I58" s="3">
-        <v>0</v>
+        <v>74969100</v>
       </c>
       <c r="J58" s="3">
-        <v>0</v>
+        <v>56995900</v>
       </c>
       <c r="K58" s="3">
         <v>0</v>
@@ -2423,69 +2689,81 @@
       <c r="N58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O58" s="3">
+        <v>0</v>
+      </c>
+      <c r="P58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>134700</v>
+        <v>20213500</v>
       </c>
       <c r="E59" s="3">
-        <v>204400</v>
+        <v>19451600</v>
       </c>
       <c r="F59" s="3">
-        <v>232600</v>
+        <v>14757100</v>
       </c>
       <c r="G59" s="3">
-        <v>555700</v>
+        <v>15426000</v>
       </c>
       <c r="H59" s="3">
-        <v>214500</v>
+        <v>22727600</v>
       </c>
       <c r="I59" s="3">
+        <v>23441600</v>
+      </c>
+      <c r="J59" s="3">
+        <v>21028000</v>
+      </c>
+      <c r="K59" s="3">
         <v>280900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>136100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>229600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>158200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>171300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>104800</v>
       </c>
     </row>
-    <row r="60" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>710983800</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>684182000</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>568990500</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>594783200</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>600716900</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>619588000</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>616963100</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -2499,84 +2777,102 @@
       <c r="N60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O60" s="3">
+        <v>0</v>
+      </c>
+      <c r="P60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>85201200</v>
+        <v>84632200</v>
       </c>
       <c r="E61" s="3">
-        <v>77764200</v>
+        <v>81441800</v>
       </c>
       <c r="F61" s="3">
-        <v>71157000</v>
+        <v>82888200</v>
       </c>
       <c r="G61" s="3">
-        <v>62829900</v>
+        <v>86645500</v>
       </c>
       <c r="H61" s="3">
-        <v>58467600</v>
+        <v>61248600</v>
       </c>
       <c r="I61" s="3">
+        <v>63172700</v>
+      </c>
+      <c r="J61" s="3">
+        <v>71184200</v>
+      </c>
+      <c r="K61" s="3">
         <v>67736500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>72139700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>78741500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>90922800</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>85466400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>85467000</v>
       </c>
     </row>
-    <row r="62" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1555800</v>
+        <v>7551800</v>
       </c>
       <c r="E62" s="3">
-        <v>1587300</v>
+        <v>7267100</v>
       </c>
       <c r="F62" s="3">
-        <v>1585900</v>
+        <v>13186200</v>
       </c>
       <c r="G62" s="3">
-        <v>1678400</v>
+        <v>13783900</v>
       </c>
       <c r="H62" s="3">
-        <v>1963300</v>
+        <v>6256700</v>
       </c>
       <c r="I62" s="3">
+        <v>6453200</v>
+      </c>
+      <c r="J62" s="3">
+        <v>10244800</v>
+      </c>
+      <c r="K62" s="3">
         <v>1934500</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>2071200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>2141800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>2270300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>3295000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>32638300</v>
       </c>
     </row>
-    <row r="63" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2613,8 +2909,14 @@
       <c r="N63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O63" s="3">
+        <v>0</v>
+      </c>
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2651,8 +2953,14 @@
       <c r="N64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O64" s="3">
+        <v>0</v>
+      </c>
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2689,46 +2997,58 @@
       <c r="N65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O65" s="3">
+        <v>0</v>
+      </c>
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>683299100</v>
+        <v>803221900</v>
       </c>
       <c r="E66" s="3">
-        <v>694530000</v>
+        <v>772943000</v>
       </c>
       <c r="F66" s="3">
-        <v>698574600</v>
+        <v>665103400</v>
       </c>
       <c r="G66" s="3">
-        <v>683586700</v>
+        <v>695252900</v>
       </c>
       <c r="H66" s="3">
-        <v>640548100</v>
+        <v>668275200</v>
       </c>
       <c r="I66" s="3">
+        <v>689268600</v>
+      </c>
+      <c r="J66" s="3">
+        <v>698445000</v>
+      </c>
+      <c r="K66" s="3">
         <v>613453200</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>640654600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>645497300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>705733500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>606513300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>606575900</v>
       </c>
     </row>
-    <row r="67" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2743,8 +3063,10 @@
       <c r="L67" s="3"/>
       <c r="M67" s="3"/>
       <c r="N67" s="3"/>
-    </row>
-    <row r="68" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O67" s="3"/>
+      <c r="P67" s="3"/>
+    </row>
+    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -2781,8 +3103,14 @@
       <c r="N68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O68" s="3">
+        <v>0</v>
+      </c>
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -2819,8 +3147,14 @@
       <c r="N69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O69" s="3">
+        <v>0</v>
+      </c>
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -2857,8 +3191,14 @@
       <c r="N70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O70" s="3">
+        <v>0</v>
+      </c>
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -2895,46 +3235,58 @@
       <c r="N71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O71" s="3">
+        <v>0</v>
+      </c>
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
-        <v>28682800</v>
+        <v>30124800</v>
       </c>
       <c r="E72" s="3">
-        <v>28292700</v>
+        <v>28989200</v>
       </c>
       <c r="F72" s="3">
-        <v>27519800</v>
+        <v>27330300</v>
       </c>
       <c r="G72" s="3">
-        <v>26659200</v>
+        <v>28569200</v>
       </c>
       <c r="H72" s="3">
-        <v>25545100</v>
+        <v>27197500</v>
       </c>
       <c r="I72" s="3">
+        <v>28051900</v>
+      </c>
+      <c r="J72" s="3">
+        <v>27525600</v>
+      </c>
+      <c r="K72" s="3">
         <v>24470600</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>23624100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>21923200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>20818900</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>21569700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>21162500</v>
       </c>
     </row>
-    <row r="73" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -2971,8 +3323,14 @@
       <c r="N73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O73" s="3">
+        <v>0</v>
+      </c>
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3009,8 +3367,14 @@
       <c r="N74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O74" s="3">
+        <v>0</v>
+      </c>
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3047,46 +3411,58 @@
       <c r="N75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O75" s="3">
+        <v>0</v>
+      </c>
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
-        <v>47126100</v>
+        <v>48434400</v>
       </c>
       <c r="E76" s="3">
-        <v>46582500</v>
+        <v>46608600</v>
       </c>
       <c r="F76" s="3">
-        <v>46287600</v>
+        <v>45278100</v>
       </c>
       <c r="G76" s="3">
-        <v>44177500</v>
+        <v>47330600</v>
       </c>
       <c r="H76" s="3">
-        <v>41389000</v>
+        <v>44844200</v>
       </c>
       <c r="I76" s="3">
+        <v>46252900</v>
+      </c>
+      <c r="J76" s="3">
+        <v>46324700</v>
+      </c>
+      <c r="K76" s="3">
         <v>42674600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>41938000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>40326800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>39782300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>40056000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>39422000</v>
       </c>
     </row>
-    <row r="77" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3123,89 +3499,107 @@
       <c r="N77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="O77" s="3">
+        <v>0</v>
+      </c>
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="I80" s="2">
+        <v>45107</v>
+      </c>
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
-        <v>44834</v>
-      </c>
-      <c r="H80" s="2">
-        <v>44651</v>
-      </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>44469</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44286</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44104</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>43921</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>43738</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="81" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3">
-        <v>2283700</v>
-      </c>
-      <c r="E81" s="3">
-        <v>2380200</v>
-      </c>
-      <c r="F81" s="3">
-        <v>2382900</v>
-      </c>
-      <c r="G81" s="3">
-        <v>2405700</v>
-      </c>
-      <c r="H81" s="3">
-        <v>2366200</v>
-      </c>
-      <c r="I81" s="3">
+      <c r="D81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="K81" s="3">
         <v>2157700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>1972700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>1337100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>1001600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>1832000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>2091000</v>
       </c>
     </row>
-    <row r="82" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3220,46 +3614,54 @@
       <c r="L82" s="3"/>
       <c r="M82" s="3"/>
       <c r="N82" s="3"/>
-    </row>
-    <row r="83" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O82" s="3"/>
+      <c r="P82" s="3"/>
+    </row>
+    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>298300</v>
+        <v>38400</v>
       </c>
       <c r="E83" s="3">
-        <v>303000</v>
+        <v>39600</v>
       </c>
       <c r="F83" s="3">
-        <v>315700</v>
+        <v>160300</v>
       </c>
       <c r="G83" s="3">
-        <v>334500</v>
+        <v>162400</v>
       </c>
       <c r="H83" s="3">
-        <v>341200</v>
+        <v>99500</v>
       </c>
       <c r="I83" s="3">
+        <v>106400</v>
+      </c>
+      <c r="J83" s="3">
+        <v>120000</v>
+      </c>
+      <c r="K83" s="3">
         <v>351200</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>377400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>511900</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>397400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>291900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>282100</v>
       </c>
     </row>
-    <row r="84" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3296,8 +3698,14 @@
       <c r="N84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O84" s="3">
+        <v>0</v>
+      </c>
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3334,8 +3742,14 @@
       <c r="N85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O85" s="3">
+        <v>0</v>
+      </c>
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3372,8 +3786,14 @@
       <c r="N86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O86" s="3">
+        <v>0</v>
+      </c>
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3410,8 +3830,14 @@
       <c r="N87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O87" s="3">
+        <v>0</v>
+      </c>
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3448,46 +3874,58 @@
       <c r="N88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O88" s="3">
+        <v>0</v>
+      </c>
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>-10454700</v>
+        <v>-7261700</v>
       </c>
       <c r="E89" s="3">
-        <v>-22099100</v>
+        <v>-6987900</v>
       </c>
       <c r="F89" s="3">
-        <v>26448000</v>
+        <v>-3601600</v>
       </c>
       <c r="G89" s="3">
-        <v>-8355300</v>
+        <v>-3764800</v>
       </c>
       <c r="H89" s="3">
-        <v>21879300</v>
+        <v>-4047600</v>
       </c>
       <c r="I89" s="3">
+        <v>-4174700</v>
+      </c>
+      <c r="J89" s="3">
+        <v>-861000</v>
+      </c>
+      <c r="K89" s="3">
         <v>9384900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>19989000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-1554900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>35427700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-7995600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>4997200</v>
       </c>
     </row>
-    <row r="90" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3502,31 +3940,33 @@
       <c r="L90" s="3"/>
       <c r="M90" s="3"/>
       <c r="N90" s="3"/>
-    </row>
-    <row r="91" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O90" s="3"/>
+      <c r="P90" s="3"/>
+    </row>
+    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="D91" s="3">
-        <v>0</v>
-      </c>
-      <c r="E91" s="3">
-        <v>0</v>
-      </c>
-      <c r="F91" s="3">
-        <v>0</v>
-      </c>
-      <c r="G91" s="3">
-        <v>0</v>
-      </c>
-      <c r="H91" s="3">
-        <v>0</v>
-      </c>
-      <c r="I91" s="3">
-        <v>0</v>
-      </c>
-      <c r="J91" s="3">
-        <v>0</v>
+      <c r="D91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="H91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="I91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="J91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="K91" s="3">
         <v>0</v>
@@ -3540,8 +3980,14 @@
       <c r="N91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O91" s="3">
+        <v>0</v>
+      </c>
+      <c r="P91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3578,8 +4024,14 @@
       <c r="N92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O92" s="3">
+        <v>0</v>
+      </c>
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3616,46 +4068,58 @@
       <c r="N93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O93" s="3">
+        <v>0</v>
+      </c>
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-13866500</v>
+        <v>-7430500</v>
       </c>
       <c r="E94" s="3">
-        <v>-1478000</v>
+        <v>-7150400</v>
       </c>
       <c r="F94" s="3">
-        <v>-5684800</v>
+        <v>-6745000</v>
       </c>
       <c r="G94" s="3">
-        <v>-1950600</v>
+        <v>-7050800</v>
       </c>
       <c r="H94" s="3">
-        <v>732600</v>
+        <v>-919900</v>
       </c>
       <c r="I94" s="3">
+        <v>-948800</v>
+      </c>
+      <c r="J94" s="3">
+        <v>-2626900</v>
+      </c>
+      <c r="K94" s="3">
         <v>7474500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-598600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-8521800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>963400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-1121600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>985900</v>
       </c>
     </row>
-    <row r="95" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3670,46 +4134,54 @@
       <c r="L95" s="3"/>
       <c r="M95" s="3"/>
       <c r="N95" s="3"/>
-    </row>
-    <row r="96" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O95" s="3"/>
+      <c r="P95" s="3"/>
+    </row>
+    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-1866100</v>
+        <v>849000</v>
       </c>
       <c r="E96" s="3">
-        <v>-1609400</v>
+        <v>817000</v>
       </c>
       <c r="F96" s="3">
-        <v>-1326500</v>
+        <v>903500</v>
       </c>
       <c r="G96" s="3">
-        <v>-1199800</v>
+        <v>944400</v>
       </c>
       <c r="H96" s="3">
-        <v>-1336600</v>
+        <v>671400</v>
       </c>
       <c r="I96" s="3">
+        <v>692500</v>
+      </c>
+      <c r="J96" s="3">
+        <v>770800</v>
+      </c>
+      <c r="K96" s="3">
         <v>-1310400</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>-589200</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>-416500</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>-1444400</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>-1468900</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>-1477500</v>
       </c>
     </row>
-    <row r="97" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -3746,8 +4218,14 @@
       <c r="N97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O97" s="3">
+        <v>0</v>
+      </c>
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -3784,8 +4262,14 @@
       <c r="N98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O98" s="3">
+        <v>0</v>
+      </c>
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -3822,118 +4306,142 @@
       <c r="N99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:14" x14ac:dyDescent="0.2">
+      <c r="O99" s="3">
+        <v>0</v>
+      </c>
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>4540600</v>
+        <v>19978500</v>
       </c>
       <c r="E100" s="3">
-        <v>-3183900</v>
+        <v>19225400</v>
       </c>
       <c r="F100" s="3">
-        <v>6123200</v>
+        <v>723800</v>
       </c>
       <c r="G100" s="3">
-        <v>6533400</v>
+        <v>756600</v>
       </c>
       <c r="H100" s="3">
-        <v>-8105300</v>
+        <v>-7913800</v>
       </c>
       <c r="I100" s="3">
+        <v>-8162400</v>
+      </c>
+      <c r="J100" s="3">
+        <v>16936200</v>
+      </c>
+      <c r="K100" s="3">
         <v>-1232000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-5251100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>368500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-643100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-3652800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>1833300</v>
       </c>
     </row>
-    <row r="101" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-633400</v>
+        <v>-232900</v>
       </c>
       <c r="E101" s="3">
-        <v>-484000</v>
+        <v>-240300</v>
       </c>
       <c r="F101" s="3">
-        <v>373400</v>
+        <v>186700</v>
       </c>
       <c r="G101" s="3">
-        <v>3824700</v>
+        <v>189300</v>
       </c>
       <c r="H101" s="3">
-        <v>-3249600</v>
+        <v>1838000</v>
       </c>
       <c r="I101" s="3">
+        <v>1965700</v>
+      </c>
+      <c r="J101" s="3">
+        <v>-1818600</v>
+      </c>
+      <c r="K101" s="3">
         <v>2336700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-3054600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>-5536400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>4104400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>1847800</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>902800</v>
       </c>
     </row>
-    <row r="102" spans="3:14" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>-20414000</v>
+        <v>4600600</v>
       </c>
       <c r="E102" s="3">
-        <v>-27245000</v>
+        <v>4427200</v>
       </c>
       <c r="F102" s="3">
-        <v>27259800</v>
+        <v>-9930900</v>
       </c>
       <c r="G102" s="3">
-        <v>52300</v>
+        <v>-10381000</v>
       </c>
       <c r="H102" s="3">
-        <v>11257000</v>
+        <v>-13114200</v>
       </c>
       <c r="I102" s="3">
+        <v>-13526100</v>
+      </c>
+      <c r="J102" s="3">
+        <v>13635100</v>
+      </c>
+      <c r="K102" s="3">
         <v>17964000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>11084800</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-23141900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>39852300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-8331100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>6128000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ANZGY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ANZGY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="267" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="311" uniqueCount="92">
   <si>
     <t>ANZGY</t>
   </si>
@@ -656,71 +656,77 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="18" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F7" s="2">
         <v>45565</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45107</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45016</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44286</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>44104</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>43921</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>43738</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -745,26 +751,32 @@
       <c r="J8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K8" s="3">
+      <c r="K8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M8" s="3">
         <v>6468400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>6621900</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>6991900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>8946500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>9955500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>10524200</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -807,8 +819,14 @@
       <c r="P9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -851,8 +869,14 @@
       <c r="P10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -869,8 +893,10 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -913,8 +939,14 @@
       <c r="P12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="R12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -957,8 +989,14 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -983,11 +1021,11 @@
       <c r="J14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1001,8 +1039,14 @@
       <c r="P14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3">
+        <v>0</v>
+      </c>
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1027,26 +1071,32 @@
       <c r="J15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K15" s="3">
+      <c r="K15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M15" s="3">
         <v>-203800</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>-223900</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>-340200</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>-221100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>-235300</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>-222100</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1060,8 +1110,10 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1086,26 +1138,32 @@
       <c r="J17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K17" s="3">
+      <c r="K17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M17" s="3">
         <v>1608000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>1610100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>3199900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>5349800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>5581100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>5972500</v>
       </c>
     </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1130,26 +1188,32 @@
       <c r="J18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K18" s="3">
+      <c r="K18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M18" s="3">
         <v>4860300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>5011800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>3792100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>3596800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>4374400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>4551700</v>
       </c>
     </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1166,8 +1230,10 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1192,26 +1258,32 @@
       <c r="J20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K20" s="3">
+      <c r="K20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M20" s="3">
         <v>-1803800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>-2078600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>-1882500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>-1902100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>-1485400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-1562500</v>
       </c>
     </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1236,26 +1308,32 @@
       <c r="J21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K21" s="3">
+      <c r="K21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M21" s="3">
         <v>3407800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>3310600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>2421400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>2092100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>3181000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>3271300</v>
       </c>
     </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1280,11 +1358,11 @@
       <c r="J22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K22" s="3">
-        <v>0</v>
-      </c>
-      <c r="L22" s="3">
-        <v>0</v>
+      <c r="K22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M22" s="3">
         <v>0</v>
@@ -1298,8 +1376,14 @@
       <c r="P22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3">
+        <v>0</v>
+      </c>
+      <c r="R22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1324,26 +1408,32 @@
       <c r="J23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K23" s="3">
+      <c r="K23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M23" s="3">
         <v>3056600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>2933200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>1909500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>1694700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>2889100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>2989200</v>
       </c>
     </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1368,26 +1458,32 @@
       <c r="J24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K24" s="3">
+      <c r="K24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M24" s="3">
         <v>892200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>955200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>567200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>634000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>873200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>846200</v>
       </c>
     </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1430,8 +1526,14 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1456,26 +1558,32 @@
       <c r="J26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K26" s="3">
+      <c r="K26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M26" s="3">
         <v>2164400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>1978100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>1342300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>1060600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>2015900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>2143100</v>
       </c>
     </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1500,26 +1608,32 @@
       <c r="J27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K27" s="3">
+      <c r="K27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M27" s="3">
         <v>2163700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>1978100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>1342300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>1060000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>2011900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>2137100</v>
       </c>
     </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1562,8 +1676,14 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1588,26 +1708,32 @@
       <c r="J29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K29" s="3">
+      <c r="K29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M29" s="3">
         <v>-6000</v>
       </c>
-      <c r="L29" s="3">
+      <c r="N29" s="3">
         <v>-5400</v>
       </c>
-      <c r="M29" s="3">
+      <c r="O29" s="3">
         <v>-5300</v>
       </c>
-      <c r="N29" s="3">
+      <c r="P29" s="3">
         <v>-58300</v>
       </c>
-      <c r="O29" s="3">
+      <c r="Q29" s="3">
         <v>-179900</v>
       </c>
-      <c r="P29" s="3">
+      <c r="R29" s="3">
         <v>-46100</v>
       </c>
     </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1650,8 +1776,14 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1694,8 +1826,14 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -1720,26 +1858,32 @@
       <c r="J32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K32" s="3">
+      <c r="K32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M32" s="3">
         <v>1803800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>2078600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>1882500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>1902100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>1485400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>1562500</v>
       </c>
     </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -1764,26 +1908,32 @@
       <c r="J33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K33" s="3">
+      <c r="K33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M33" s="3">
         <v>2157700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>1972700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>1337100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>1001600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>1832000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>2091000</v>
       </c>
     </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1826,8 +1976,14 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -1852,75 +2008,87 @@
       <c r="J35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K35" s="3">
+      <c r="K35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M35" s="3">
         <v>2157700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>1972700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>1337100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>1001600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>1832000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>2091000</v>
       </c>
     </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F38" s="2">
         <v>45565</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45107</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45016</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44286</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>44104</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>43921</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>43738</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1937,8 +2105,10 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1955,126 +2125,140 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>122109900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>121165300</v>
+      </c>
+      <c r="F41" s="3">
         <v>74077500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>71285000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>89792000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>93862300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>88044800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>90810600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>140012100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>110479500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>94031000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>79933200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>101864800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>61620500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>70159800</v>
       </c>
     </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>59434300</v>
+      </c>
+      <c r="E42" s="3">
+        <v>58974600</v>
+      </c>
+      <c r="F42" s="3">
         <v>100013900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>96243700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>58639100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>61297200</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>83320000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>85937400</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>57148100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>62063100</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>109296400</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>131963200</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>155272400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>117856900</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>88366600</v>
       </c>
     </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>159700</v>
+      </c>
+      <c r="E43" s="3">
+        <v>158400</v>
+      </c>
+      <c r="F43" s="3">
         <v>31900</v>
-      </c>
-      <c r="E43" s="3">
-        <v>30700</v>
-      </c>
-      <c r="F43" s="3">
-        <v>29300</v>
       </c>
       <c r="G43" s="3">
         <v>30700</v>
       </c>
       <c r="H43" s="3">
+        <v>29300</v>
+      </c>
+      <c r="I43" s="3">
+        <v>30700</v>
+      </c>
+      <c r="J43" s="3">
         <v>73600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>75900</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>32900</v>
       </c>
-      <c r="K43" s="3">
-        <v>0</v>
-      </c>
-      <c r="L43" s="3">
-        <v>0</v>
-      </c>
       <c r="M43" s="3">
         <v>0</v>
       </c>
@@ -2087,8 +2271,14 @@
       <c r="P43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3">
+        <v>0</v>
+      </c>
+      <c r="R43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2113,11 +2303,11 @@
       <c r="J44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2131,38 +2321,44 @@
       <c r="P44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3">
+        <v>0</v>
+      </c>
+      <c r="R44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>10408500</v>
+      </c>
+      <c r="E45" s="3">
+        <v>10328000</v>
+      </c>
+      <c r="F45" s="3">
         <v>10798000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>10391000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>7857800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>8214000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>11555100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>11918100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>10906600</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
@@ -2175,38 +2371,44 @@
       <c r="P45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3">
+        <v>0</v>
+      </c>
+      <c r="R45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>192514000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>191024800</v>
+      </c>
+      <c r="F46" s="3">
         <v>185382400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>178394000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>156772100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>163878700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>183410300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>189172000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>208532800</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -2219,140 +2421,164 @@
       <c r="P46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3">
+        <v>0</v>
+      </c>
+      <c r="R46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>97837700</v>
+      </c>
+      <c r="E47" s="3">
+        <v>97080900</v>
+      </c>
+      <c r="F47" s="3">
         <v>98449000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>94737800</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>77615300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>81133600</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>64385400</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>66408000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>64524200</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>1321800</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>1242700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>1423900</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>1499500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>1948700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>1803700</v>
       </c>
     </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1354600</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1344100</v>
+      </c>
+      <c r="F48" s="3">
         <v>1540600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>1482500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>1495300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>1563100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>1324800</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>1366400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>1534900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>1832600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>1871500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>1982600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>2081700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>1267900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>1227700</v>
       </c>
     </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3657900</v>
+      </c>
+      <c r="E49" s="3">
+        <v>3629600</v>
+      </c>
+      <c r="F49" s="3">
         <v>3821000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>3676900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>2547800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>2663300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>2618600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>2700800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>2707000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>2764300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>2697300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>2881400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>3213600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>3203400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>3306200</v>
       </c>
     </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2395,8 +2621,14 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2439,52 +2671,64 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3550000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>3522500</v>
+      </c>
+      <c r="F52" s="3">
         <v>3727400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>3586900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>3576800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>3738900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>3311000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>3415000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>3094600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>1567800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>1411000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>1397600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>1177300</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>2100200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>29454000</v>
       </c>
     </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2527,52 +2771,64 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>812404300</v>
+      </c>
+      <c r="E54" s="3">
+        <v>806119800</v>
+      </c>
+      <c r="F54" s="3">
         <v>852190900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>820066100</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>710882300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>743107000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>713456200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>735868900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>745121700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>656127800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>682592600</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>685824200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>745515800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>646569300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>645997900</v>
       </c>
     </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2589,8 +2845,10 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2607,82 +2865,90 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>567708000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>563316400</v>
+      </c>
+      <c r="F57" s="3">
         <v>593473600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>571101500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>496752500</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>519270600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>504355700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>520199700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>538939200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>5796100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>5736400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>6006200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>6830500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>5250900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>5035400</v>
       </c>
     </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>66256100</v>
+      </c>
+      <c r="E58" s="3">
+        <v>65743500</v>
+      </c>
+      <c r="F58" s="3">
         <v>95871900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>92257800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>57480900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>60086600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>72685700</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>74969100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>56995900</v>
       </c>
-      <c r="K58" s="3">
-        <v>0</v>
-      </c>
-      <c r="L58" s="3">
-        <v>0</v>
-      </c>
       <c r="M58" s="3">
         <v>0</v>
       </c>
@@ -2695,82 +2961,94 @@
       <c r="P58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3">
+        <v>0</v>
+      </c>
+      <c r="R58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>16594700</v>
+      </c>
+      <c r="E59" s="3">
+        <v>16466400</v>
+      </c>
+      <c r="F59" s="3">
         <v>20213500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>19451600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>14757100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>15426000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>22727600</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>23441600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>21028000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>280900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>136100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>229600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>158200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>171300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>104800</v>
       </c>
     </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>650558800</v>
+      </c>
+      <c r="E60" s="3">
+        <v>645526300</v>
+      </c>
+      <c r="F60" s="3">
         <v>710983800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>684182000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>568990500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>594783200</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>600716900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>619588000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>616963100</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -2783,96 +3061,114 @@
       <c r="P60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3">
+        <v>0</v>
+      </c>
+      <c r="R60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>105747200</v>
+      </c>
+      <c r="E61" s="3">
+        <v>104929100</v>
+      </c>
+      <c r="F61" s="3">
         <v>84632200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>81441800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>82888200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>86645500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>61248600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>63172700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>71184200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>67736500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>72139700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>78741500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>90922800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>85466400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>85467000</v>
       </c>
     </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>10859400</v>
+      </c>
+      <c r="E62" s="3">
+        <v>10775400</v>
+      </c>
+      <c r="F62" s="3">
         <v>7551800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>7267100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>13186200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>13783900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>6256700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>6453200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>10244800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>1934500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>2071200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>2141800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>2270300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>3295000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>32638300</v>
       </c>
     </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2915,8 +3211,14 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2959,8 +3261,14 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3003,52 +3311,64 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>767293300</v>
+      </c>
+      <c r="E66" s="3">
+        <v>761357800</v>
+      </c>
+      <c r="F66" s="3">
         <v>803221900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>772943000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>665103400</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>695252900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>668275200</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>689268600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>698445000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>613453200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>640654600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>645497300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>705733500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>606513300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>606575900</v>
       </c>
     </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3065,8 +3385,10 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3109,8 +3431,14 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3153,8 +3481,14 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3197,8 +3531,14 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3241,52 +3581,64 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>27876400</v>
+      </c>
+      <c r="E72" s="3">
+        <v>27660700</v>
+      </c>
+      <c r="F72" s="3">
         <v>30124800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>28989200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>27330300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>28569200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>27197500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>28051900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>27525600</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>24470600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>23624100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>21923200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>20818900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>21569700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>21162500</v>
       </c>
     </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3329,8 +3681,14 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3373,8 +3731,14 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3417,52 +3781,64 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>44634500</v>
+      </c>
+      <c r="E76" s="3">
+        <v>44289300</v>
+      </c>
+      <c r="F76" s="3">
         <v>48434400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>46608600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>45278100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>47330600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>44844200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>46252900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>46324700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>42674600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>41938000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>40326800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>39782300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>40056000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>39422000</v>
       </c>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3505,57 +3881,69 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45747</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="F80" s="2">
         <v>45565</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45107</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45016</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44286</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>44104</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>43921</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>43738</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -3580,26 +3968,32 @@
       <c r="J81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K81" s="3">
+      <c r="K81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="M81" s="3">
         <v>2157700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>1972700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>1337100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>1001600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>1832000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>2091000</v>
       </c>
     </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3616,52 +4010,60 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>145100</v>
+      </c>
+      <c r="E83" s="3">
+        <v>151700</v>
+      </c>
+      <c r="F83" s="3">
         <v>38400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>39600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>160300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>162400</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>99500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>106400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>120000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>351200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>377400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>511900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>397400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>291900</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>282100</v>
       </c>
     </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3704,8 +4106,14 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3748,8 +4156,14 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3792,8 +4206,14 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3836,8 +4256,14 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3880,52 +4306,64 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-1328100</v>
+      </c>
+      <c r="E89" s="3">
+        <v>-1317800</v>
+      </c>
+      <c r="F89" s="3">
         <v>-7261700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-6987900</v>
       </c>
-      <c r="F89" s="3">
-        <v>-3601600</v>
-      </c>
-      <c r="G89" s="3">
-        <v>-3764800</v>
-      </c>
       <c r="H89" s="3">
+        <v>-3620800</v>
+      </c>
+      <c r="I89" s="3">
+        <v>-3784900</v>
+      </c>
+      <c r="J89" s="3">
         <v>-4047600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-4174700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-861000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>9384900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>19989000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-1554900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>35427700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>-7995600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>4997200</v>
       </c>
     </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3942,8 +4380,10 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -3968,11 +4408,11 @@
       <c r="J91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="K91" s="3">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3">
-        <v>0</v>
+      <c r="K91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="L91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="M91" s="3">
         <v>0</v>
@@ -3986,8 +4426,14 @@
       <c r="P91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3">
+        <v>0</v>
+      </c>
+      <c r="R91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4030,8 +4476,14 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4074,52 +4526,64 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-3201300</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-3176600</v>
+      </c>
+      <c r="F94" s="3">
         <v>-7430500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-7150400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-6745000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-7050800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-919900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-948800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-2626900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>7474500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-598600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-8521800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>963400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-1121600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>985900</v>
       </c>
     </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4136,52 +4600,60 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>756500</v>
+      </c>
+      <c r="E96" s="3">
+        <v>750700</v>
+      </c>
+      <c r="F96" s="3">
         <v>849000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>817000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>903500</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>944400</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>671400</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>692500</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>770800</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>-1310400</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>-589200</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>-416500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>-1444400</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>-1468900</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>-1477500</v>
       </c>
     </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4224,8 +4696,14 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4268,8 +4746,14 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4312,136 +4796,160 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>17024800</v>
+      </c>
+      <c r="E100" s="3">
+        <v>16893100</v>
+      </c>
+      <c r="F100" s="3">
         <v>19978500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>19225400</v>
       </c>
-      <c r="F100" s="3">
-        <v>723800</v>
-      </c>
-      <c r="G100" s="3">
-        <v>756600</v>
-      </c>
       <c r="H100" s="3">
+        <v>744000</v>
+      </c>
+      <c r="I100" s="3">
+        <v>777800</v>
+      </c>
+      <c r="J100" s="3">
         <v>-7913800</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-8162400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>16936200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-1232000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-5251100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>368500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-643100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-3652800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>1833300</v>
       </c>
     </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-308100</v>
+      </c>
+      <c r="E101" s="3">
+        <v>-322100</v>
+      </c>
+      <c r="F101" s="3">
         <v>-232900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-240300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>186700</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>189300</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>1838000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>1965700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-1818600</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>2336700</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-3054600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-5536400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>4104400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>1847800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>902800</v>
       </c>
     </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>13977800</v>
+      </c>
+      <c r="E102" s="3">
+        <v>13869700</v>
+      </c>
+      <c r="F102" s="3">
         <v>4600600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>4427200</v>
       </c>
-      <c r="F102" s="3">
-        <v>-9930900</v>
-      </c>
-      <c r="G102" s="3">
-        <v>-10381000</v>
-      </c>
       <c r="H102" s="3">
+        <v>-9929900</v>
+      </c>
+      <c r="I102" s="3">
+        <v>-10380000</v>
+      </c>
+      <c r="J102" s="3">
         <v>-13114200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>-13526100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>13635100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>17964000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>11084800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-23141900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>39852300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-8331100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>6128000</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/ANZGY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/ANZGY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="399" uniqueCount="92">
   <si>
     <t>ANZGY</t>
   </si>
@@ -656,83 +656,89 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:T102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="20" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="22" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F7" s="2">
         <v>45930</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45838</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45747</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45565</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45107</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>45016</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -769,26 +775,32 @@
       <c r="N8" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O8" s="3">
+      <c r="O8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q8" s="3">
         <v>6468400</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>6621900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>6991900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>8946500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>9955500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>10524200</v>
       </c>
     </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -843,8 +855,14 @@
       <c r="T9" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V9" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>6</v>
       </c>
@@ -899,8 +917,14 @@
       <c r="T10" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V10" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>7</v>
       </c>
@@ -921,8 +945,10 @@
       <c r="R11" s="3"/>
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="3"/>
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>8</v>
       </c>
@@ -977,8 +1003,14 @@
       <c r="T12" s="3" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="V12" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1033,8 +1065,14 @@
       <c r="T13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="3">
+        <v>0</v>
+      </c>
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1071,11 +1109,11 @@
       <c r="N14" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
-      </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1089,8 +1127,14 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1127,26 +1171,32 @@
       <c r="N15" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O15" s="3">
+      <c r="O15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q15" s="3">
         <v>-203800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>-223900</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="S15" s="3">
         <v>-340200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="T15" s="3">
         <v>-221100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="U15" s="3">
         <v>-235300</v>
       </c>
-      <c r="T15" s="3">
+      <c r="V15" s="3">
         <v>-222100</v>
       </c>
     </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1164,8 +1214,10 @@
       <c r="R16" s="3"/>
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
-    </row>
-    <row r="17" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="3"/>
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1202,26 +1254,32 @@
       <c r="N17" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O17" s="3">
+      <c r="O17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q17" s="3">
         <v>1608000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>1610100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>3199900</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>5349800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>5581100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>5972500</v>
       </c>
     </row>
-    <row r="18" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1258,26 +1316,32 @@
       <c r="N18" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O18" s="3">
+      <c r="O18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q18" s="3">
         <v>4860300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>5011800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>3792100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>3596800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>4374400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>4551700</v>
       </c>
     </row>
-    <row r="19" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1298,8 +1362,10 @@
       <c r="R19" s="3"/>
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
-    </row>
-    <row r="20" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="3"/>
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -1336,26 +1402,32 @@
       <c r="N20" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O20" s="3">
+      <c r="O20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q20" s="3">
         <v>-1803800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>-2078600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>-1882500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>-1902100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>-1485400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>-1562500</v>
       </c>
     </row>
-    <row r="21" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -1392,26 +1464,32 @@
       <c r="N21" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q21" s="3">
         <v>3407800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="R21" s="3">
         <v>3310600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>2421400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>2092100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>3181000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>3271300</v>
       </c>
     </row>
-    <row r="22" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1448,11 +1526,11 @@
       <c r="N22" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O22" s="3">
-        <v>0</v>
-      </c>
-      <c r="P22" s="3">
-        <v>0</v>
+      <c r="O22" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q22" s="3">
         <v>0</v>
@@ -1466,8 +1544,14 @@
       <c r="T22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="3">
+        <v>0</v>
+      </c>
+      <c r="V22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -1504,26 +1588,32 @@
       <c r="N23" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O23" s="3">
+      <c r="O23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q23" s="3">
         <v>3056600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>2933200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>1909500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>1694700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>2889100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>2989200</v>
       </c>
     </row>
-    <row r="24" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -1560,26 +1650,32 @@
       <c r="N24" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O24" s="3">
+      <c r="O24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q24" s="3">
         <v>892200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>955200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>567200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>634000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>873200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>846200</v>
       </c>
     </row>
-    <row r="25" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1634,8 +1730,14 @@
       <c r="T25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="3">
+        <v>0</v>
+      </c>
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -1672,26 +1774,32 @@
       <c r="N26" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O26" s="3">
+      <c r="O26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q26" s="3">
         <v>2164400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>1978100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>1342300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>1060600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>2015900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>2143100</v>
       </c>
     </row>
-    <row r="27" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -1728,26 +1836,32 @@
       <c r="N27" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O27" s="3">
+      <c r="O27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q27" s="3">
         <v>2163700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>1978100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>1342300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>1060000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>2011900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>2137100</v>
       </c>
     </row>
-    <row r="28" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1802,8 +1916,14 @@
       <c r="T28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="3">
+        <v>0</v>
+      </c>
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1840,26 +1960,32 @@
       <c r="N29" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O29" s="3">
+      <c r="O29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q29" s="3">
         <v>-6000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="R29" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="S29" s="3">
         <v>-5300</v>
       </c>
-      <c r="R29" s="3">
+      <c r="T29" s="3">
         <v>-58300</v>
       </c>
-      <c r="S29" s="3">
+      <c r="U29" s="3">
         <v>-179900</v>
       </c>
-      <c r="T29" s="3">
+      <c r="V29" s="3">
         <v>-46100</v>
       </c>
     </row>
-    <row r="30" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1914,8 +2040,14 @@
       <c r="T30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1970,8 +2102,14 @@
       <c r="T31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="3">
+        <v>0</v>
+      </c>
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -2008,26 +2146,32 @@
       <c r="N32" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O32" s="3">
+      <c r="O32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q32" s="3">
         <v>1803800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>2078600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>1882500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>1902100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>1485400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>1562500</v>
       </c>
     </row>
-    <row r="33" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -2064,26 +2208,32 @@
       <c r="N33" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O33" s="3">
+      <c r="O33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q33" s="3">
         <v>2157700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>1972700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>1337100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>1001600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>1832000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>2091000</v>
       </c>
     </row>
-    <row r="34" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2138,8 +2288,14 @@
       <c r="T34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="3">
+        <v>0</v>
+      </c>
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -2176,87 +2332,99 @@
       <c r="N35" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O35" s="3">
+      <c r="O35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q35" s="3">
         <v>2157700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>1972700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>1337100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>1001600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>1832000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>2091000</v>
       </c>
     </row>
-    <row r="37" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F38" s="2">
         <v>45930</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45838</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45747</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45565</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45107</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>45016</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="39" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2277,8 +2445,10 @@
       <c r="R39" s="3"/>
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
-    </row>
-    <row r="40" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U39" s="3"/>
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2299,162 +2469,176 @@
       <c r="R40" s="3"/>
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
-    </row>
-    <row r="41" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U40" s="3"/>
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>113610900</v>
+      </c>
+      <c r="E41" s="3">
+        <v>110418200</v>
+      </c>
+      <c r="F41" s="3">
         <v>65337000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>64763000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>122109900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>121165300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>74077500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>71285000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>89792000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>93862300</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>88044800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>90810600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>140012100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>110479500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>94031000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>79933200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>101864800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>61620500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>70159800</v>
       </c>
     </row>
-    <row r="42" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>81764100</v>
+      </c>
+      <c r="E42" s="3">
+        <v>79466400</v>
+      </c>
+      <c r="F42" s="3">
         <v>100638900</v>
       </c>
-      <c r="E42" s="3">
+      <c r="G42" s="3">
         <v>99754800</v>
       </c>
-      <c r="F42" s="3">
+      <c r="H42" s="3">
         <v>59434300</v>
       </c>
-      <c r="G42" s="3">
+      <c r="I42" s="3">
         <v>58974600</v>
       </c>
-      <c r="H42" s="3">
+      <c r="J42" s="3">
         <v>100013900</v>
       </c>
-      <c r="I42" s="3">
+      <c r="K42" s="3">
         <v>96243700</v>
       </c>
-      <c r="J42" s="3">
+      <c r="L42" s="3">
         <v>58639100</v>
       </c>
-      <c r="K42" s="3">
+      <c r="M42" s="3">
         <v>61297200</v>
       </c>
-      <c r="L42" s="3">
+      <c r="N42" s="3">
         <v>83320000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="O42" s="3">
         <v>85937400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="P42" s="3">
         <v>57148100</v>
       </c>
-      <c r="O42" s="3">
+      <c r="Q42" s="3">
         <v>62063100</v>
       </c>
-      <c r="P42" s="3">
+      <c r="R42" s="3">
         <v>109296400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="S42" s="3">
         <v>131963200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="T42" s="3">
         <v>155272400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="U42" s="3">
         <v>117856900</v>
       </c>
-      <c r="T42" s="3">
+      <c r="V42" s="3">
         <v>88366600</v>
       </c>
     </row>
-    <row r="43" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>65200</v>
+      </c>
+      <c r="E43" s="3">
+        <v>63400</v>
+      </c>
+      <c r="F43" s="3">
         <v>21800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>21600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>159700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>158400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>31900</v>
-      </c>
-      <c r="I43" s="3">
-        <v>30700</v>
-      </c>
-      <c r="J43" s="3">
-        <v>29300</v>
       </c>
       <c r="K43" s="3">
         <v>30700</v>
       </c>
       <c r="L43" s="3">
+        <v>29300</v>
+      </c>
+      <c r="M43" s="3">
+        <v>30700</v>
+      </c>
+      <c r="N43" s="3">
         <v>73600</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>75900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>32900</v>
       </c>
-      <c r="O43" s="3">
-        <v>0</v>
-      </c>
-      <c r="P43" s="3">
-        <v>0</v>
-      </c>
       <c r="Q43" s="3">
         <v>0</v>
       </c>
@@ -2467,8 +2651,14 @@
       <c r="T43" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="44" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U43" s="3">
+        <v>0</v>
+      </c>
+      <c r="V43" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2505,11 +2695,11 @@
       <c r="N44" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -2523,50 +2713,56 @@
       <c r="T44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U44" s="3">
+        <v>0</v>
+      </c>
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>16859900</v>
+      </c>
+      <c r="E45" s="3">
+        <v>16386100</v>
+      </c>
+      <c r="F45" s="3">
         <v>21975700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>21782600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>10408500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>10328000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>10798000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>10391000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>7857800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>8214000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>11555100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>11918100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>10906600</v>
       </c>
-      <c r="O45" s="3">
-        <v>0</v>
-      </c>
-      <c r="P45" s="3">
-        <v>0</v>
-      </c>
       <c r="Q45" s="3">
         <v>0</v>
       </c>
@@ -2579,50 +2775,56 @@
       <c r="T45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U45" s="3">
+        <v>0</v>
+      </c>
+      <c r="V45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>212691200</v>
+      </c>
+      <c r="E46" s="3">
+        <v>206714200</v>
+      </c>
+      <c r="F46" s="3">
         <v>188331200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>186676700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>192514000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>191024800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>185382400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>178394000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>156772100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>163878700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>183410300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>189172000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>208532800</v>
       </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
       <c r="Q46" s="3">
         <v>0</v>
       </c>
@@ -2635,176 +2837,200 @@
       <c r="T46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U46" s="3">
+        <v>0</v>
+      </c>
+      <c r="V46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>113737200</v>
+      </c>
+      <c r="E47" s="3">
+        <v>110541000</v>
+      </c>
+      <c r="F47" s="3">
         <v>110347900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>109378500</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>97837700</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>97080900</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>98449000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>94737800</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>77615300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>81133600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>64385400</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>66408000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>64524200</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>1321800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>1242700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>1423900</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>1499500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>1948700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>1803700</v>
       </c>
     </row>
-    <row r="48" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>1365100</v>
+      </c>
+      <c r="E48" s="3">
+        <v>1326700</v>
+      </c>
+      <c r="F48" s="3">
         <v>1418100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>1405600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>1354600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>1344100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>1540600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>1482500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>1495300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>1563100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>1324800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>1366400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>1534900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>1832600</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>1871500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>1982600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>2081700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>1267900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>1227700</v>
       </c>
     </row>
-    <row r="49" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>3832300</v>
+      </c>
+      <c r="E49" s="3">
+        <v>3724700</v>
+      </c>
+      <c r="F49" s="3">
         <v>3813100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>3779600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>3657900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>3629600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>3821000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>3676900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>2547800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>2663300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>2618600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>2700800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>2707000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>2764300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>2697300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>2881400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>3213600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>3203400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>3306200</v>
       </c>
     </row>
-    <row r="50" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2859,8 +3085,14 @@
       <c r="T50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U50" s="3">
+        <v>0</v>
+      </c>
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2915,64 +3147,76 @@
       <c r="T51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U51" s="3">
+        <v>0</v>
+      </c>
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>3586000</v>
+      </c>
+      <c r="E52" s="3">
+        <v>3485200</v>
+      </c>
+      <c r="F52" s="3">
         <v>3229700</v>
       </c>
-      <c r="E52" s="3">
+      <c r="G52" s="3">
         <v>3201300</v>
       </c>
-      <c r="F52" s="3">
+      <c r="H52" s="3">
         <v>3550000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>3522500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>3727400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>3586900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>3576800</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>3738900</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>3311000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>3415000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>3094600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>1567800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>1411000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>1397600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>1177300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>2100200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>29454000</v>
       </c>
     </row>
-    <row r="53" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3027,64 +3271,76 @@
       <c r="T53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U53" s="3">
+        <v>0</v>
+      </c>
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>901676000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>876337400</v>
+      </c>
+      <c r="F54" s="3">
         <v>857932400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>850395300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>812404300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>806119800</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>852190900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>820066100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>710882300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>743107000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>713456200</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>735868900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>745121700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>656127800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>682592600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>685824200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>745515800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>646569300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>645997900</v>
       </c>
     </row>
-    <row r="55" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3105,8 +3361,10 @@
       <c r="R55" s="3"/>
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
-    </row>
-    <row r="56" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U55" s="3"/>
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3127,106 +3385,114 @@
       <c r="R56" s="3"/>
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
-    </row>
-    <row r="57" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U56" s="3"/>
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>623363300</v>
+      </c>
+      <c r="E57" s="3">
+        <v>605845800</v>
+      </c>
+      <c r="F57" s="3">
         <v>598994600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>593732400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>567708000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>563316400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>593473600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>571101500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>496752500</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>519270600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>504355700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>520199700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>538939200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="Q57" s="3">
         <v>5796100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="R57" s="3">
         <v>5736400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="S57" s="3">
         <v>6006200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="T57" s="3">
         <v>6830500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="U57" s="3">
         <v>5250900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="V57" s="3">
         <v>5035400</v>
       </c>
     </row>
-    <row r="58" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>76594800</v>
+      </c>
+      <c r="E58" s="3">
+        <v>74442400</v>
+      </c>
+      <c r="F58" s="3">
         <v>90426000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>89631500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>66256100</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>65743500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>95871900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>92257800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>57480900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>60086600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>72685700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>74969100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>56995900</v>
       </c>
-      <c r="O58" s="3">
-        <v>0</v>
-      </c>
-      <c r="P58" s="3">
-        <v>0</v>
-      </c>
       <c r="Q58" s="3">
         <v>0</v>
       </c>
@@ -3239,106 +3505,118 @@
       <c r="T58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U58" s="3">
+        <v>0</v>
+      </c>
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>30181800</v>
+      </c>
+      <c r="E59" s="3">
+        <v>29333600</v>
+      </c>
+      <c r="F59" s="3">
         <v>28486700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>28236400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>16594700</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>16466400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>20213500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>19451600</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>14757100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>15426000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>22727600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>23441600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>21028000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>280900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>136100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>229600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>158200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>171300</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>104800</v>
       </c>
     </row>
-    <row r="60" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>730139900</v>
+      </c>
+      <c r="E60" s="3">
+        <v>709621800</v>
+      </c>
+      <c r="F60" s="3">
         <v>719300200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>712981100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>650558800</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>645526300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>710983800</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>684182000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>568990500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>594783200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>600716900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>619588000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>616963100</v>
       </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
-      <c r="P60" s="3">
-        <v>0</v>
-      </c>
       <c r="Q60" s="3">
         <v>0</v>
       </c>
@@ -3351,120 +3629,138 @@
       <c r="T60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U60" s="3">
+        <v>0</v>
+      </c>
+      <c r="V60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>110138800</v>
+      </c>
+      <c r="E61" s="3">
+        <v>107043800</v>
+      </c>
+      <c r="F61" s="3">
         <v>84007500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>83269500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>105747200</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>104929100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>84632200</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>81441800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>82888200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>86645500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>61248600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>63172700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>71184200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>67736500</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>72139700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>78741500</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>90922800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>85466400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>85467000</v>
       </c>
     </row>
-    <row r="62" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>11978800</v>
+      </c>
+      <c r="E62" s="3">
+        <v>11642200</v>
+      </c>
+      <c r="F62" s="3">
         <v>6939600</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>6878600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>10859400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>10775400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>7551800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>7267100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>13186200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>13783900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>6256700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>6453200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>10244800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>1934500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>2071200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>2141800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>2270300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>3295000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>32638300</v>
       </c>
     </row>
-    <row r="63" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3519,8 +3815,14 @@
       <c r="T63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U63" s="3">
+        <v>0</v>
+      </c>
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3575,8 +3877,14 @@
       <c r="T64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U64" s="3">
+        <v>0</v>
+      </c>
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3631,64 +3939,76 @@
       <c r="T65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U65" s="3">
+        <v>0</v>
+      </c>
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>852429200</v>
+      </c>
+      <c r="E66" s="3">
+        <v>828474500</v>
+      </c>
+      <c r="F66" s="3">
         <v>810398200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>803278700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>767293300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>761357800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>803221900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>772943000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>665103400</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>695252900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>668275200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>689268600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>698445000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>613453200</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>640654600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>645497300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>705733500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>606513300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>606575900</v>
       </c>
     </row>
-    <row r="67" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3709,8 +4029,10 @@
       <c r="R67" s="3"/>
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
-    </row>
-    <row r="68" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U67" s="3"/>
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3765,8 +4087,14 @@
       <c r="T68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U68" s="3">
+        <v>0</v>
+      </c>
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3821,8 +4149,14 @@
       <c r="T69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U69" s="3">
+        <v>0</v>
+      </c>
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3877,8 +4211,14 @@
       <c r="T70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U70" s="3">
+        <v>0</v>
+      </c>
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3933,64 +4273,76 @@
       <c r="T71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U71" s="3">
+        <v>0</v>
+      </c>
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>31395200</v>
+      </c>
+      <c r="E72" s="3">
+        <v>30512900</v>
+      </c>
+      <c r="F72" s="3">
         <v>29427900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>29169300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>27876400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>27660700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>30124800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>28989200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>27330300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>28569200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>27197500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>28051900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>27525600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>24470600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>23624100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>21923200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>20818900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>21569700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>21162500</v>
       </c>
     </row>
-    <row r="73" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4045,8 +4397,14 @@
       <c r="T73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U73" s="3">
+        <v>0</v>
+      </c>
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4101,8 +4459,14 @@
       <c r="T74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U74" s="3">
+        <v>0</v>
+      </c>
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4157,64 +4521,76 @@
       <c r="T75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U75" s="3">
+        <v>0</v>
+      </c>
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>48764300</v>
+      </c>
+      <c r="E76" s="3">
+        <v>47393900</v>
+      </c>
+      <c r="F76" s="3">
         <v>47045400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>46632100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>44634500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>44289300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>48434400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>46608600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>45278100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>47330600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>44844200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>46252900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>46324700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>42674600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>41938000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>40326800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>39782300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>40056000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>39422000</v>
       </c>
     </row>
-    <row r="77" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4269,69 +4645,81 @@
       <c r="T77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:20" x14ac:dyDescent="0.2">
+      <c r="U77" s="3">
+        <v>0</v>
+      </c>
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:20" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46112</v>
+      </c>
+      <c r="E80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="F80" s="2">
         <v>45930</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45838</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45747</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45565</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45107</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>45016</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="81" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -4368,26 +4756,32 @@
       <c r="N81" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O81" s="3">
+      <c r="O81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P81" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="Q81" s="3">
         <v>2157700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>1972700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>1337100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>1001600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>1832000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>2091000</v>
       </c>
     </row>
-    <row r="82" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4408,64 +4802,72 @@
       <c r="R82" s="3"/>
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
-    </row>
-    <row r="83" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U82" s="3"/>
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>167500</v>
+      </c>
+      <c r="E83" s="3">
+        <v>166200</v>
+      </c>
+      <c r="F83" s="3">
         <v>52300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="G83" s="3">
         <v>50400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
         <v>145100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="I83" s="3">
         <v>151700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="J83" s="3">
         <v>38400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="K83" s="3">
         <v>39600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="L83" s="3">
         <v>160300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="M83" s="3">
         <v>162400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="N83" s="3">
         <v>99500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="O83" s="3">
         <v>106400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>120000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="Q83" s="3">
         <v>351200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="R83" s="3">
         <v>377400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="S83" s="3">
         <v>511900</v>
       </c>
-      <c r="R83" s="3">
+      <c r="T83" s="3">
         <v>397400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="U83" s="3">
         <v>291900</v>
       </c>
-      <c r="T83" s="3">
+      <c r="V83" s="3">
         <v>282100</v>
       </c>
     </row>
-    <row r="84" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4520,8 +4922,14 @@
       <c r="T84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U84" s="3">
+        <v>0</v>
+      </c>
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4576,8 +4984,14 @@
       <c r="T85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U85" s="3">
+        <v>0</v>
+      </c>
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4632,8 +5046,14 @@
       <c r="T86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U86" s="3">
+        <v>0</v>
+      </c>
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4688,8 +5108,14 @@
       <c r="T87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U87" s="3">
+        <v>0</v>
+      </c>
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4744,64 +5170,76 @@
       <c r="T88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U88" s="3">
+        <v>0</v>
+      </c>
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>827000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>803800</v>
+      </c>
+      <c r="F89" s="3">
         <v>-6626100</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>-6567900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-1328100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-1317800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>-7241200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>-6968200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-3620800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-3784900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>-4047600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-4174700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-861000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>9384900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>19989000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-1554900</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>35427700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>-7995600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>4997200</v>
       </c>
     </row>
-    <row r="90" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4822,8 +5260,10 @@
       <c r="R90" s="3"/>
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
-    </row>
-    <row r="91" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U90" s="3"/>
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -4860,11 +5300,11 @@
       <c r="N91" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="O91" s="3">
-        <v>0</v>
-      </c>
-      <c r="P91" s="3">
-        <v>0</v>
+      <c r="O91" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="P91" s="3" t="s">
+        <v>5</v>
       </c>
       <c r="Q91" s="3">
         <v>0</v>
@@ -4878,8 +5318,14 @@
       <c r="T91" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="92" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U91" s="3">
+        <v>0</v>
+      </c>
+      <c r="V91" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4934,8 +5380,14 @@
       <c r="T92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U92" s="3">
+        <v>0</v>
+      </c>
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4990,64 +5442,76 @@
       <c r="T93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U93" s="3">
+        <v>0</v>
+      </c>
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-802600</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-780100</v>
+      </c>
+      <c r="F94" s="3">
         <v>-4520800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-4481100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-3201300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-3176600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-7430500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-7150400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-6745000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-7050800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-919900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-948800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-2626900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>7474500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-598600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-8521800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>963400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-1121600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>985900</v>
       </c>
     </row>
-    <row r="95" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5068,64 +5532,72 @@
       <c r="R95" s="3"/>
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
-    </row>
-    <row r="96" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U95" s="3"/>
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>826000</v>
+      </c>
+      <c r="E96" s="3">
+        <v>802800</v>
+      </c>
+      <c r="F96" s="3">
         <v>710000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>703800</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>756500</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>750700</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>849000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>817000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>903500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>944400</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>671400</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>692500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>770800</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>-1310400</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>-589200</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-416500</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-1444400</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-1468900</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-1477500</v>
       </c>
     </row>
-    <row r="97" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5180,8 +5652,14 @@
       <c r="T97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U97" s="3">
+        <v>0</v>
+      </c>
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5236,8 +5714,14 @@
       <c r="T98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U98" s="3">
+        <v>0</v>
+      </c>
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5292,172 +5776,196 @@
       <c r="T99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:20" x14ac:dyDescent="0.2">
+      <c r="U99" s="3">
+        <v>0</v>
+      </c>
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>5452400</v>
+      </c>
+      <c r="E100" s="3">
+        <v>5299200</v>
+      </c>
+      <c r="F100" s="3">
         <v>-1183300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-1172900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>17024800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>16893100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>19957000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>19204700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>744000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>777800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-7913800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-8162400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>16936200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>-1232000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-5251100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>368500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-643100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>-3652800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>1833300</v>
       </c>
     </row>
-    <row r="101" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>1482500</v>
+      </c>
+      <c r="E101" s="3">
+        <v>1471000</v>
+      </c>
+      <c r="F101" s="3">
         <v>-685700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-659900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>-308100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>-322100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-232900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-240300</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>186700</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>189300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>1838000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>1965700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-1818600</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>2336700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-3054600</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-5536400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>4104400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>1847800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>902800</v>
       </c>
     </row>
-    <row r="102" spans="3:20" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>3544100</v>
+      </c>
+      <c r="E102" s="3">
+        <v>3444500</v>
+      </c>
+      <c r="F102" s="3">
         <v>-13420200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-13302300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>13977800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>13869700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>4599600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>4426200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-9929900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-10380000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>-13114200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-13526100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>13635100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>17964000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>11084800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-23141900</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>39852300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>-8331100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>6128000</v>
       </c>
     </row>
